--- a/research/traditional_assets/database/data/reunion/reunion_food_processing.xlsx
+++ b/research/traditional_assets/database/data/reunion/reunion_food_processing.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtpa_almer" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0526</v>
+        <v>0.00908</v>
+      </c>
+      <c r="E2">
+        <v>-0.07629999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.03582306018854242</v>
+        <v>0.1055753262158956</v>
       </c>
       <c r="H2">
-        <v>-0.03582306018854242</v>
+        <v>0.1055753262158956</v>
       </c>
       <c r="I2">
-        <v>-0.1856366669776456</v>
+        <v>0.1184495173866913</v>
       </c>
       <c r="J2">
-        <v>-0.1856366669776456</v>
+        <v>0.1184495173866913</v>
       </c>
       <c r="K2">
-        <v>-29.9</v>
+        <v>12.1</v>
       </c>
       <c r="L2">
-        <v>-0.2168237853517041</v>
+        <v>0.07176749703440095</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V2">
-        <v>0.2094395280235988</v>
+        <v>0.1626984126984127</v>
       </c>
       <c r="W2">
-        <v>-0.3314855875831486</v>
+        <v>0.1782032400589101</v>
       </c>
       <c r="X2">
-        <v>0.3417015850501658</v>
+        <v>0.1764319312732953</v>
       </c>
       <c r="Y2">
-        <v>-0.6731871726333144</v>
+        <v>0.001771308785614878</v>
       </c>
       <c r="Z2">
-        <v>0.6078867056829977</v>
+        <v>0.7516482199576732</v>
       </c>
       <c r="AA2">
-        <v>-0.1128460619430127</v>
+        <v>0.08903236889855201</v>
       </c>
       <c r="AB2">
-        <v>0.1034072589676326</v>
+        <v>0.0887823153273874</v>
       </c>
       <c r="AC2">
-        <v>-0.2162533209106453</v>
+        <v>0.0002500535711646157</v>
       </c>
       <c r="AD2">
-        <v>167.3</v>
+        <v>111.9</v>
       </c>
       <c r="AE2">
-        <v>0.5714818810866453</v>
+        <v>0.1970568430192092</v>
       </c>
       <c r="AF2">
-        <v>167.8714818810867</v>
+        <v>112.0970568430192</v>
       </c>
       <c r="AG2">
-        <v>160.7714818810867</v>
+        <v>103.8970568430192</v>
       </c>
       <c r="AH2">
-        <v>0.8319881497426933</v>
+        <v>0.6898405363200574</v>
       </c>
       <c r="AI2">
-        <v>0.7120092750053378</v>
+        <v>0.6644873297779638</v>
       </c>
       <c r="AJ2">
-        <v>0.8258604718450363</v>
+        <v>0.6733573469824727</v>
       </c>
       <c r="AK2">
-        <v>0.7030674772322102</v>
+        <v>0.6473455581471506</v>
       </c>
       <c r="AL2">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AM2">
-        <v>1.974</v>
+        <v>1.94</v>
       </c>
       <c r="AN2">
-        <v>-38.68208092485549</v>
+        <v>3.233169604160647</v>
       </c>
       <c r="AO2">
-        <v>-13.11557788944724</v>
+        <v>10.20618556701031</v>
       </c>
       <c r="AP2">
-        <v>-37.17259696672524</v>
+        <v>3.001937499075967</v>
       </c>
       <c r="AQ2">
-        <v>-13.22188449848024</v>
+        <v>10.20618556701031</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0526</v>
+        <v>0.00908</v>
+      </c>
+      <c r="E3">
+        <v>-0.07629999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.03582306018854242</v>
+        <v>0.1055753262158956</v>
       </c>
       <c r="H3">
-        <v>-0.03582306018854242</v>
+        <v>0.1055753262158956</v>
       </c>
       <c r="I3">
-        <v>-0.1856366669776456</v>
+        <v>0.1184495173866913</v>
       </c>
       <c r="J3">
-        <v>-0.1856366669776456</v>
+        <v>0.1184495173866913</v>
       </c>
       <c r="K3">
-        <v>-29.9</v>
+        <v>12.1</v>
       </c>
       <c r="L3">
-        <v>-0.2168237853517041</v>
+        <v>0.07176749703440095</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V3">
-        <v>0.2094395280235988</v>
+        <v>0.1626984126984127</v>
       </c>
       <c r="W3">
-        <v>-0.3314855875831486</v>
+        <v>0.1782032400589101</v>
       </c>
       <c r="X3">
-        <v>0.3417015850501658</v>
+        <v>0.1764319312732953</v>
       </c>
       <c r="Y3">
-        <v>-0.6731871726333144</v>
+        <v>0.001771308785614878</v>
       </c>
       <c r="Z3">
-        <v>0.6078867056829977</v>
+        <v>0.7516482199576732</v>
       </c>
       <c r="AA3">
-        <v>-0.1128460619430127</v>
+        <v>0.08903236889855201</v>
       </c>
       <c r="AB3">
-        <v>0.1034072589676326</v>
+        <v>0.0887823153273874</v>
       </c>
       <c r="AC3">
-        <v>-0.2162533209106453</v>
+        <v>0.0002500535711646157</v>
       </c>
       <c r="AD3">
-        <v>167.3</v>
+        <v>111.9</v>
       </c>
       <c r="AE3">
-        <v>0.5714818810866453</v>
+        <v>0.1970568430192092</v>
       </c>
       <c r="AF3">
-        <v>167.8714818810867</v>
+        <v>112.0970568430192</v>
       </c>
       <c r="AG3">
-        <v>160.7714818810867</v>
+        <v>103.8970568430192</v>
       </c>
       <c r="AH3">
-        <v>0.8319881497426933</v>
+        <v>0.6898405363200574</v>
       </c>
       <c r="AI3">
-        <v>0.7120092750053378</v>
+        <v>0.6644873297779638</v>
       </c>
       <c r="AJ3">
-        <v>0.8258604718450363</v>
+        <v>0.6733573469824727</v>
       </c>
       <c r="AK3">
-        <v>0.7030674772322102</v>
+        <v>0.6473455581471506</v>
       </c>
       <c r="AL3">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AM3">
-        <v>1.974</v>
+        <v>1.94</v>
       </c>
       <c r="AN3">
-        <v>-38.68208092485549</v>
+        <v>3.233169604160647</v>
       </c>
       <c r="AO3">
-        <v>-13.11557788944724</v>
+        <v>10.20618556701031</v>
       </c>
       <c r="AP3">
-        <v>-37.17259696672524</v>
+        <v>3.001937499075967</v>
       </c>
       <c r="AQ3">
-        <v>-13.22188449848024</v>
+        <v>10.20618556701031</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sapmer SA (ENXTPA:ALMER)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTPA:ALMER</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Food Processing</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Reunion</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.689840536320057</v>
+      </c>
+      <c r="F2">
+        <v>0.54</v>
+      </c>
+      <c r="G2">
+        <v>50.4</v>
+      </c>
+      <c r="H2">
+        <v>80.0424866195672</v>
+      </c>
+      <c r="I2">
+        <v>154.297056843019</v>
+      </c>
+      <c r="J2">
+        <v>159.590897314798</v>
+      </c>
+      <c r="K2">
+        <v>112.097056843019</v>
+      </c>
+      <c r="L2">
+        <v>87.7484106952304</v>
+      </c>
+      <c r="M2">
+        <v>0.0887823153273874</v>
+      </c>
+      <c r="N2">
+        <v>0.08477804671516211</v>
+      </c>
+      <c r="O2">
+        <v>0.0493741384484879</v>
+      </c>
+      <c r="P2">
+        <v>0.0413440980831854</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.176431931273295</v>
+      </c>
+      <c r="T2">
+        <v>0.135765725544004</v>
+      </c>
+      <c r="U2">
+        <v>1.85459804056051</v>
+      </c>
+      <c r="V2">
+        <v>1.30661862353981</v>
+      </c>
+      <c r="W2">
+        <v>4.581279556119082</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>50.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.07421119200131308</v>
+      </c>
+      <c r="AC2">
+        <v>0.06568235227197405</v>
+      </c>
+      <c r="AD2">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>34.61</v>
+      </c>
+      <c r="AH2">
+        <v>12.5</v>
+      </c>
+      <c r="AI2">
+        <v>9.880000000000003</v>
+      </c>
+      <c r="AJ2">
+        <v>112.0970568430192</v>
+      </c>
+      <c r="AK2">
+        <v>111.9</v>
+      </c>
+      <c r="AL2">
+        <v>1.94</v>
+      </c>
+      <c r="AM2">
+        <v>111.9</v>
+      </c>
+      <c r="AN2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09031057175801477</v>
+      </c>
+      <c r="C2">
+        <v>160.5680679680315</v>
+      </c>
+      <c r="D2">
+        <v>152.3680679680315</v>
+      </c>
+      <c r="E2">
+        <v>-112.0970568430192</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H2">
+        <v>50.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>34.61</v>
+      </c>
+      <c r="K2">
+        <v>12.5</v>
+      </c>
+      <c r="L2">
+        <v>22.11</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>22.11</v>
+      </c>
+      <c r="O2">
+        <v>5.489672570559454</v>
+      </c>
+      <c r="P2">
+        <v>16.62032742944055</v>
+      </c>
+      <c r="Q2">
+        <v>29.12032742944055</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09031057175801477</v>
+      </c>
+      <c r="T2">
+        <v>0.6941078612118687</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W2">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09013820847925023</v>
+      </c>
+      <c r="C3">
+        <v>159.1582404618488</v>
+      </c>
+      <c r="D3">
+        <v>152.583211030279</v>
+      </c>
+      <c r="E3">
+        <v>-110.472086274589</v>
+      </c>
+      <c r="F3">
+        <v>1.624970568430192</v>
+      </c>
+      <c r="G3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H3">
+        <v>50.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>34.61</v>
+      </c>
+      <c r="K3">
+        <v>12.5</v>
+      </c>
+      <c r="L3">
+        <v>22.11</v>
+      </c>
+      <c r="M3">
+        <v>0.07426115497725978</v>
+      </c>
+      <c r="N3">
+        <v>22.03573884502274</v>
+      </c>
+      <c r="O3">
+        <v>5.471234333312202</v>
+      </c>
+      <c r="P3">
+        <v>16.56450451171054</v>
+      </c>
+      <c r="Q3">
+        <v>29.06450451171054</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09070169354517442</v>
+      </c>
+      <c r="T3">
+        <v>0.6993782493650833</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W3">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>297.7330477390301</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.0899658452004857</v>
+      </c>
+      <c r="C4">
+        <v>157.7490213769273</v>
+      </c>
+      <c r="D4">
+        <v>152.7989625137877</v>
+      </c>
+      <c r="E4">
+        <v>-108.8471157061588</v>
+      </c>
+      <c r="F4">
+        <v>3.249941136860384</v>
+      </c>
+      <c r="G4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H4">
+        <v>50.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>34.61</v>
+      </c>
+      <c r="K4">
+        <v>12.5</v>
+      </c>
+      <c r="L4">
+        <v>22.11</v>
+      </c>
+      <c r="M4">
+        <v>0.1485223099545196</v>
+      </c>
+      <c r="N4">
+        <v>21.96147769004548</v>
+      </c>
+      <c r="O4">
+        <v>5.452796096064951</v>
+      </c>
+      <c r="P4">
+        <v>16.50868159398053</v>
+      </c>
+      <c r="Q4">
+        <v>29.00868159398053</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09110079740962304</v>
+      </c>
+      <c r="T4">
+        <v>0.7047561964602003</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W4">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>148.866523869515</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08979348192172117</v>
+      </c>
+      <c r="C5">
+        <v>156.3404132978305</v>
+      </c>
+      <c r="D5">
+        <v>153.0153250031211</v>
+      </c>
+      <c r="E5">
+        <v>-107.2221451377286</v>
+      </c>
+      <c r="F5">
+        <v>4.874911705290576</v>
+      </c>
+      <c r="G5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H5">
+        <v>50.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>34.61</v>
+      </c>
+      <c r="K5">
+        <v>12.5</v>
+      </c>
+      <c r="L5">
+        <v>22.11</v>
+      </c>
+      <c r="M5">
+        <v>0.2227834649317794</v>
+      </c>
+      <c r="N5">
+        <v>21.88721653506822</v>
+      </c>
+      <c r="O5">
+        <v>5.434357858817699</v>
+      </c>
+      <c r="P5">
+        <v>16.45285867625052</v>
+      </c>
+      <c r="Q5">
+        <v>28.95285867625052</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09150813021973041</v>
+      </c>
+      <c r="T5">
+        <v>0.710245029062433</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W5">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>99.24434924634336</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08962111864295665</v>
+      </c>
+      <c r="C6">
+        <v>154.9324188237815</v>
+      </c>
+      <c r="D6">
+        <v>153.2323010975022</v>
+      </c>
+      <c r="E6">
+        <v>-105.5971745692984</v>
+      </c>
+      <c r="F6">
+        <v>6.499882273720768</v>
+      </c>
+      <c r="G6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H6">
+        <v>50.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>34.61</v>
+      </c>
+      <c r="K6">
+        <v>12.5</v>
+      </c>
+      <c r="L6">
+        <v>22.11</v>
+      </c>
+      <c r="M6">
+        <v>0.2970446199090391</v>
+      </c>
+      <c r="N6">
+        <v>21.81295538009096</v>
+      </c>
+      <c r="O6">
+        <v>5.415919621570448</v>
+      </c>
+      <c r="P6">
+        <v>16.39703575852051</v>
+      </c>
+      <c r="Q6">
+        <v>28.89703575852051</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09192394913004835</v>
+      </c>
+      <c r="T6">
+        <v>0.7158482123438791</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W6">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>74.43326193475752</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08944875536419211</v>
+      </c>
+      <c r="C7">
+        <v>153.5250405687671</v>
+      </c>
+      <c r="D7">
+        <v>153.4498934109181</v>
+      </c>
+      <c r="E7">
+        <v>-103.9722040008683</v>
+      </c>
+      <c r="F7">
+        <v>8.124852842150961</v>
+      </c>
+      <c r="G7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H7">
+        <v>50.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>34.61</v>
+      </c>
+      <c r="K7">
+        <v>12.5</v>
+      </c>
+      <c r="L7">
+        <v>22.11</v>
+      </c>
+      <c r="M7">
+        <v>0.371305774886299</v>
+      </c>
+      <c r="N7">
+        <v>21.7386942251137</v>
+      </c>
+      <c r="O7">
+        <v>5.397481384323196</v>
+      </c>
+      <c r="P7">
+        <v>16.3412128407905</v>
+      </c>
+      <c r="Q7">
+        <v>28.8412128407905</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09234852212268876</v>
+      </c>
+      <c r="T7">
+        <v>0.7215693573786186</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W7">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>59.54660954780601</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08927639208542761</v>
+      </c>
+      <c r="C8">
+        <v>152.118281161643</v>
+      </c>
+      <c r="D8">
+        <v>153.6681045722242</v>
+      </c>
+      <c r="E8">
+        <v>-102.3472334324381</v>
+      </c>
+      <c r="F8">
+        <v>9.749823410581152</v>
+      </c>
+      <c r="G8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H8">
+        <v>50.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>34.61</v>
+      </c>
+      <c r="K8">
+        <v>12.5</v>
+      </c>
+      <c r="L8">
+        <v>22.11</v>
+      </c>
+      <c r="M8">
+        <v>0.4455669298635587</v>
+      </c>
+      <c r="N8">
+        <v>21.66443307013644</v>
+      </c>
+      <c r="O8">
+        <v>5.379043147075945</v>
+      </c>
+      <c r="P8">
+        <v>16.2853899230605</v>
+      </c>
+      <c r="Q8">
+        <v>28.7853899230605</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09278212858325771</v>
+      </c>
+      <c r="T8">
+        <v>0.727412228903459</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W8">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>49.62217462317168</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08910402880666306</v>
+      </c>
+      <c r="C9">
+        <v>150.7121432462395</v>
+      </c>
+      <c r="D9">
+        <v>153.8869372252509</v>
+      </c>
+      <c r="E9">
+        <v>-100.7222628640079</v>
+      </c>
+      <c r="F9">
+        <v>11.37479397901135</v>
+      </c>
+      <c r="G9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H9">
+        <v>50.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>34.61</v>
+      </c>
+      <c r="K9">
+        <v>12.5</v>
+      </c>
+      <c r="L9">
+        <v>22.11</v>
+      </c>
+      <c r="M9">
+        <v>0.5198280848408185</v>
+      </c>
+      <c r="N9">
+        <v>21.59017191515918</v>
+      </c>
+      <c r="O9">
+        <v>5.360604909828694</v>
+      </c>
+      <c r="P9">
+        <v>16.22956700533049</v>
+      </c>
+      <c r="Q9">
+        <v>28.72956700533049</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09322505991394639</v>
+      </c>
+      <c r="T9">
+        <v>0.7333807535793712</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W9">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>42.53329253414715</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08893166552789852</v>
+      </c>
+      <c r="C10">
+        <v>149.306629481468</v>
+      </c>
+      <c r="D10">
+        <v>154.1063940289096</v>
+      </c>
+      <c r="E10">
+        <v>-99.09729229557769</v>
+      </c>
+      <c r="F10">
+        <v>12.99976454744154</v>
+      </c>
+      <c r="G10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H10">
+        <v>50.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>34.61</v>
+      </c>
+      <c r="K10">
+        <v>12.5</v>
+      </c>
+      <c r="L10">
+        <v>22.11</v>
+      </c>
+      <c r="M10">
+        <v>0.5940892398180783</v>
+      </c>
+      <c r="N10">
+        <v>21.51591076018192</v>
+      </c>
+      <c r="O10">
+        <v>5.342166672581442</v>
+      </c>
+      <c r="P10">
+        <v>16.17374408760048</v>
+      </c>
+      <c r="Q10">
+        <v>28.67374408760048</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09367762018660658</v>
+      </c>
+      <c r="T10">
+        <v>0.7394790287917163</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W10">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>37.21663096737876</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08875930224913399</v>
+      </c>
+      <c r="C11">
+        <v>147.9017425414293</v>
+      </c>
+      <c r="D11">
+        <v>154.326477657301</v>
+      </c>
+      <c r="E11">
+        <v>-97.47232172714749</v>
+      </c>
+      <c r="F11">
+        <v>14.62473511587173</v>
+      </c>
+      <c r="G11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H11">
+        <v>50.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>34.61</v>
+      </c>
+      <c r="K11">
+        <v>12.5</v>
+      </c>
+      <c r="L11">
+        <v>22.11</v>
+      </c>
+      <c r="M11">
+        <v>0.668350394795338</v>
+      </c>
+      <c r="N11">
+        <v>21.44164960520466</v>
+      </c>
+      <c r="O11">
+        <v>5.323728435334191</v>
+      </c>
+      <c r="P11">
+        <v>16.11792116987047</v>
+      </c>
+      <c r="Q11">
+        <v>28.61792116987047</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09414012683888567</v>
+      </c>
+      <c r="T11">
+        <v>0.7457113320307063</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W11">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>33.08144974878113</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08858693897036947</v>
+      </c>
+      <c r="C12">
+        <v>146.4974851155216</v>
+      </c>
+      <c r="D12">
+        <v>154.5471907998235</v>
+      </c>
+      <c r="E12">
+        <v>-95.84735115871729</v>
+      </c>
+      <c r="F12">
+        <v>16.24970568430192</v>
+      </c>
+      <c r="G12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H12">
+        <v>50.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>34.61</v>
+      </c>
+      <c r="K12">
+        <v>12.5</v>
+      </c>
+      <c r="L12">
+        <v>22.11</v>
+      </c>
+      <c r="M12">
+        <v>0.7426115497725979</v>
+      </c>
+      <c r="N12">
+        <v>21.3673884502274</v>
+      </c>
+      <c r="O12">
+        <v>5.30529019808694</v>
+      </c>
+      <c r="P12">
+        <v>16.06209825214046</v>
+      </c>
+      <c r="Q12">
+        <v>28.56209825214046</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09461291141677097</v>
+      </c>
+      <c r="T12">
+        <v>0.7520821308972294</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W12">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>29.77330477390301</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08841457569160494</v>
+      </c>
+      <c r="C13">
+        <v>145.0938599085505</v>
+      </c>
+      <c r="D13">
+        <v>154.7685361612826</v>
+      </c>
+      <c r="E13">
+        <v>-94.2223805902871</v>
+      </c>
+      <c r="F13">
+        <v>17.87467625273211</v>
+      </c>
+      <c r="G13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H13">
+        <v>50.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>34.61</v>
+      </c>
+      <c r="K13">
+        <v>12.5</v>
+      </c>
+      <c r="L13">
+        <v>22.11</v>
+      </c>
+      <c r="M13">
+        <v>0.8168727047498576</v>
+      </c>
+      <c r="N13">
+        <v>21.29312729525014</v>
+      </c>
+      <c r="O13">
+        <v>5.286851960839688</v>
+      </c>
+      <c r="P13">
+        <v>16.00627533441045</v>
+      </c>
+      <c r="Q13">
+        <v>28.50627533441045</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09509632036719302</v>
+      </c>
+      <c r="T13">
+        <v>0.7585960937832251</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W13">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>27.06664070354819</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08824221241284042</v>
+      </c>
+      <c r="C14">
+        <v>143.6908696408393</v>
+      </c>
+      <c r="D14">
+        <v>154.9905164620016</v>
+      </c>
+      <c r="E14">
+        <v>-92.59741002185692</v>
+      </c>
+      <c r="F14">
+        <v>19.4996468211623</v>
+      </c>
+      <c r="G14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H14">
+        <v>50.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>34.61</v>
+      </c>
+      <c r="K14">
+        <v>12.5</v>
+      </c>
+      <c r="L14">
+        <v>22.11</v>
+      </c>
+      <c r="M14">
+        <v>0.8911338597271174</v>
+      </c>
+      <c r="N14">
+        <v>21.21886614027288</v>
+      </c>
+      <c r="O14">
+        <v>5.268413723592437</v>
+      </c>
+      <c r="P14">
+        <v>15.95045241668045</v>
+      </c>
+      <c r="Q14">
+        <v>28.45045241668045</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09559071588467012</v>
+      </c>
+      <c r="T14">
+        <v>0.7652581012802661</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W14">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>24.81108731158584</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08806984913407588</v>
+      </c>
+      <c r="C15">
+        <v>142.2885170483403</v>
+      </c>
+      <c r="D15">
+        <v>155.2131344379328</v>
+      </c>
+      <c r="E15">
+        <v>-90.97243945342672</v>
+      </c>
+      <c r="F15">
+        <v>21.1246173895925</v>
+      </c>
+      <c r="G15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H15">
+        <v>50.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>34.61</v>
+      </c>
+      <c r="K15">
+        <v>12.5</v>
+      </c>
+      <c r="L15">
+        <v>22.11</v>
+      </c>
+      <c r="M15">
+        <v>0.9653950147043773</v>
+      </c>
+      <c r="N15">
+        <v>21.14460498529562</v>
+      </c>
+      <c r="O15">
+        <v>5.249975486345186</v>
+      </c>
+      <c r="P15">
+        <v>15.89462949895044</v>
+      </c>
+      <c r="Q15">
+        <v>28.39462949895044</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09609647681634208</v>
+      </c>
+      <c r="T15">
+        <v>0.77207325837494</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W15">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>22.90254213377154</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08789748585531135</v>
+      </c>
+      <c r="C16">
+        <v>140.8868048827476</v>
+      </c>
+      <c r="D16">
+        <v>155.4363928407703</v>
+      </c>
+      <c r="E16">
+        <v>-89.34746888499653</v>
+      </c>
+      <c r="F16">
+        <v>22.74958795802269</v>
+      </c>
+      <c r="G16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H16">
+        <v>50.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>34.61</v>
+      </c>
+      <c r="K16">
+        <v>12.5</v>
+      </c>
+      <c r="L16">
+        <v>22.11</v>
+      </c>
+      <c r="M16">
+        <v>1.039656169681637</v>
+      </c>
+      <c r="N16">
+        <v>21.07034383031836</v>
+      </c>
+      <c r="O16">
+        <v>5.231537249097934</v>
+      </c>
+      <c r="P16">
+        <v>15.83880658122043</v>
+      </c>
+      <c r="Q16">
+        <v>28.33880658122043</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09661399963014596</v>
+      </c>
+      <c r="T16">
+        <v>0.7790469074950717</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W16">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>21.26664626707358</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08772512257654681</v>
+      </c>
+      <c r="C17">
+        <v>139.48573591161</v>
+      </c>
+      <c r="D17">
+        <v>155.6602944380629</v>
+      </c>
+      <c r="E17">
+        <v>-87.72249831656634</v>
+      </c>
+      <c r="F17">
+        <v>24.37455852645288</v>
+      </c>
+      <c r="G17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H17">
+        <v>50.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>34.61</v>
+      </c>
+      <c r="K17">
+        <v>12.5</v>
+      </c>
+      <c r="L17">
+        <v>22.11</v>
+      </c>
+      <c r="M17">
+        <v>1.113917324658897</v>
+      </c>
+      <c r="N17">
+        <v>20.9960826753411</v>
+      </c>
+      <c r="O17">
+        <v>5.213099011850683</v>
+      </c>
+      <c r="P17">
+        <v>15.78298366349042</v>
+      </c>
+      <c r="Q17">
+        <v>28.28298366349042</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09714369945133346</v>
+      </c>
+      <c r="T17">
+        <v>0.7861846424768535</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W17">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>19.84886984926867</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08755275929778229</v>
+      </c>
+      <c r="C18">
+        <v>138.0853129184459</v>
+      </c>
+      <c r="D18">
+        <v>155.884842013329</v>
+      </c>
+      <c r="E18">
+        <v>-86.09752774813614</v>
+      </c>
+      <c r="F18">
+        <v>25.99952909488307</v>
+      </c>
+      <c r="G18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H18">
+        <v>50.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>34.61</v>
+      </c>
+      <c r="K18">
+        <v>12.5</v>
+      </c>
+      <c r="L18">
+        <v>22.11</v>
+      </c>
+      <c r="M18">
+        <v>1.188178479636157</v>
+      </c>
+      <c r="N18">
+        <v>20.92182152036384</v>
+      </c>
+      <c r="O18">
+        <v>5.194660774603431</v>
+      </c>
+      <c r="P18">
+        <v>15.72716074576041</v>
+      </c>
+      <c r="Q18">
+        <v>28.22716074576041</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09768601117302542</v>
+      </c>
+      <c r="T18">
+        <v>0.7934923235296301</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W18">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>18.60831548368938</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08738039601901776</v>
+      </c>
+      <c r="C19">
+        <v>136.6855387028581</v>
+      </c>
+      <c r="D19">
+        <v>156.1100383661714</v>
+      </c>
+      <c r="E19">
+        <v>-84.47255717970594</v>
+      </c>
+      <c r="F19">
+        <v>27.62449966331327</v>
+      </c>
+      <c r="G19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H19">
+        <v>50.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>34.61</v>
+      </c>
+      <c r="K19">
+        <v>12.5</v>
+      </c>
+      <c r="L19">
+        <v>22.11</v>
+      </c>
+      <c r="M19">
+        <v>1.262439634613416</v>
+      </c>
+      <c r="N19">
+        <v>20.84756036538658</v>
+      </c>
+      <c r="O19">
+        <v>5.17622253735618</v>
+      </c>
+      <c r="P19">
+        <v>15.6713378280304</v>
+      </c>
+      <c r="Q19">
+        <v>28.1713378280304</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.0982413906470473</v>
+      </c>
+      <c r="T19">
+        <v>0.8009760932824735</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W19">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>17.51370869053118</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08720803274025324</v>
+      </c>
+      <c r="C20">
+        <v>135.2864160806504</v>
+      </c>
+      <c r="D20">
+        <v>156.3358863123938</v>
+      </c>
+      <c r="E20">
+        <v>-82.84758661127576</v>
+      </c>
+      <c r="F20">
+        <v>29.24947023174346</v>
+      </c>
+      <c r="G20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H20">
+        <v>50.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>34.61</v>
+      </c>
+      <c r="K20">
+        <v>12.5</v>
+      </c>
+      <c r="L20">
+        <v>22.11</v>
+      </c>
+      <c r="M20">
+        <v>1.336700789590676</v>
+      </c>
+      <c r="N20">
+        <v>20.77329921040932</v>
+      </c>
+      <c r="O20">
+        <v>5.157784300108928</v>
+      </c>
+      <c r="P20">
+        <v>15.61551491030039</v>
+      </c>
+      <c r="Q20">
+        <v>28.11551491030039</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09881031596189899</v>
+      </c>
+      <c r="T20">
+        <v>0.8086423940048986</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W20">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>16.54072487439056</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08703566946148872</v>
+      </c>
+      <c r="C21">
+        <v>133.8879478839449</v>
+      </c>
+      <c r="D21">
+        <v>156.5623886841186</v>
+      </c>
+      <c r="E21">
+        <v>-81.22261604284557</v>
+      </c>
+      <c r="F21">
+        <v>30.87444080017365</v>
+      </c>
+      <c r="G21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H21">
+        <v>50.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>34.61</v>
+      </c>
+      <c r="K21">
+        <v>12.5</v>
+      </c>
+      <c r="L21">
+        <v>22.11</v>
+      </c>
+      <c r="M21">
+        <v>1.410961944567936</v>
+      </c>
+      <c r="N21">
+        <v>20.69903805543206</v>
+      </c>
+      <c r="O21">
+        <v>5.139346062861677</v>
+      </c>
+      <c r="P21">
+        <v>15.55969199257039</v>
+      </c>
+      <c r="Q21">
+        <v>28.05969199257039</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.099393288815389</v>
+      </c>
+      <c r="T21">
+        <v>0.8164979861031859</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W21">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>15.67016040731737</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08686330618272417</v>
+      </c>
+      <c r="C22">
+        <v>132.490136961301</v>
+      </c>
+      <c r="D22">
+        <v>156.7895483299048</v>
+      </c>
+      <c r="E22">
+        <v>-79.59764547441537</v>
+      </c>
+      <c r="F22">
+        <v>32.49941136860384</v>
+      </c>
+      <c r="G22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H22">
+        <v>50.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>34.61</v>
+      </c>
+      <c r="K22">
+        <v>12.5</v>
+      </c>
+      <c r="L22">
+        <v>22.11</v>
+      </c>
+      <c r="M22">
+        <v>1.485223099545196</v>
+      </c>
+      <c r="N22">
+        <v>20.6247769004548</v>
+      </c>
+      <c r="O22">
+        <v>5.120907825614426</v>
+      </c>
+      <c r="P22">
+        <v>15.50386907484038</v>
+      </c>
+      <c r="Q22">
+        <v>28.00386907484038</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09999083599021624</v>
+      </c>
+      <c r="T22">
+        <v>0.8245499680039303</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W22">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>14.8866523869515</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08669094290395965</v>
+      </c>
+      <c r="C23">
+        <v>131.0929861778334</v>
+      </c>
+      <c r="D23">
+        <v>157.0173681148674</v>
+      </c>
+      <c r="E23">
+        <v>-77.97267490598519</v>
+      </c>
+      <c r="F23">
+        <v>34.12438193703403</v>
+      </c>
+      <c r="G23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H23">
+        <v>50.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>34.61</v>
+      </c>
+      <c r="K23">
+        <v>12.5</v>
+      </c>
+      <c r="L23">
+        <v>22.11</v>
+      </c>
+      <c r="M23">
+        <v>1.559484254522455</v>
+      </c>
+      <c r="N23">
+        <v>20.55051574547754</v>
+      </c>
+      <c r="O23">
+        <v>5.102469588367175</v>
+      </c>
+      <c r="P23">
+        <v>15.44804615711037</v>
+      </c>
+      <c r="Q23">
+        <v>27.94804615711037</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1006035109416214</v>
+      </c>
+      <c r="T23">
+        <v>0.8328057975477318</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W23">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>14.17776417804905</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08651857962519513</v>
+      </c>
+      <c r="C24">
+        <v>129.696498415334</v>
+      </c>
+      <c r="D24">
+        <v>157.2458509207982</v>
+      </c>
+      <c r="E24">
+        <v>-76.347704337555</v>
+      </c>
+      <c r="F24">
+        <v>35.74935250546422</v>
+      </c>
+      <c r="G24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H24">
+        <v>50.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>34.61</v>
+      </c>
+      <c r="K24">
+        <v>12.5</v>
+      </c>
+      <c r="L24">
+        <v>22.11</v>
+      </c>
+      <c r="M24">
+        <v>1.633745409499715</v>
+      </c>
+      <c r="N24">
+        <v>20.47625459050028</v>
+      </c>
+      <c r="O24">
+        <v>5.084031351119923</v>
+      </c>
+      <c r="P24">
+        <v>15.39222323938036</v>
+      </c>
+      <c r="Q24">
+        <v>27.89222323938036</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1012318955071652</v>
+      </c>
+      <c r="T24">
+        <v>0.8412733150285537</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W24">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>13.53332035177409</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08634621634643058</v>
+      </c>
+      <c r="C25">
+        <v>128.3006765723927</v>
+      </c>
+      <c r="D25">
+        <v>157.4749996462871</v>
+      </c>
+      <c r="E25">
+        <v>-74.7227337691248</v>
+      </c>
+      <c r="F25">
+        <v>37.37432307389442</v>
+      </c>
+      <c r="G25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H25">
+        <v>50.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>34.61</v>
+      </c>
+      <c r="K25">
+        <v>12.5</v>
+      </c>
+      <c r="L25">
+        <v>22.11</v>
+      </c>
+      <c r="M25">
+        <v>1.708006564476975</v>
+      </c>
+      <c r="N25">
+        <v>20.40199343552302</v>
+      </c>
+      <c r="O25">
+        <v>5.065593113872672</v>
+      </c>
+      <c r="P25">
+        <v>15.33640032165035</v>
+      </c>
+      <c r="Q25">
+        <v>27.83640032165035</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.101876601749736</v>
+      </c>
+      <c r="T25">
+        <v>0.849960768028358</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W25">
+        <v>0.0343531869527559</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>12.94491511908826</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08646251004337412</v>
+      </c>
+      <c r="C26">
+        <v>126.5210258837589</v>
+      </c>
+      <c r="D26">
+        <v>157.3203195260835</v>
+      </c>
+      <c r="E26">
+        <v>-73.0977632006946</v>
+      </c>
+      <c r="F26">
+        <v>38.99929364232461</v>
+      </c>
+      <c r="G26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H26">
+        <v>50.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>34.61</v>
+      </c>
+      <c r="K26">
+        <v>12.5</v>
+      </c>
+      <c r="L26">
+        <v>22.11</v>
+      </c>
+      <c r="M26">
+        <v>1.844666589281954</v>
+      </c>
+      <c r="N26">
+        <v>20.26533341071805</v>
+      </c>
+      <c r="O26">
+        <v>5.031661915787468</v>
+      </c>
+      <c r="P26">
+        <v>15.23367149493058</v>
+      </c>
+      <c r="Q26">
+        <v>27.73367149493058</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1025382739460587</v>
+      </c>
+      <c r="T26">
+        <v>0.8588768382123677</v>
+      </c>
+      <c r="U26">
+        <v>0.0473</v>
+      </c>
+      <c r="V26">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W26">
+        <v>0.03555592435153948</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.98590581542783</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08630217413859742</v>
+      </c>
+      <c r="C27">
+        <v>125.1093946099242</v>
+      </c>
+      <c r="D27">
+        <v>157.533658820679</v>
+      </c>
+      <c r="E27">
+        <v>-71.47279263226442</v>
+      </c>
+      <c r="F27">
+        <v>40.6242642107548</v>
+      </c>
+      <c r="G27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H27">
+        <v>50.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>34.61</v>
+      </c>
+      <c r="K27">
+        <v>12.5</v>
+      </c>
+      <c r="L27">
+        <v>22.11</v>
+      </c>
+      <c r="M27">
+        <v>1.921527697168702</v>
+      </c>
+      <c r="N27">
+        <v>20.1884723028313</v>
+      </c>
+      <c r="O27">
+        <v>5.012578138505301</v>
+      </c>
+      <c r="P27">
+        <v>15.175894164326</v>
+      </c>
+      <c r="Q27">
+        <v>27.675894164326</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1032175907342834</v>
+      </c>
+      <c r="T27">
+        <v>0.8680306702679509</v>
+      </c>
+      <c r="U27">
+        <v>0.0473</v>
+      </c>
+      <c r="V27">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W27">
+        <v>0.03555592435153948</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>11.50646958281072</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08614183823382073</v>
+      </c>
+      <c r="C28">
+        <v>123.6983427330654</v>
+      </c>
+      <c r="D28">
+        <v>157.7475775122504</v>
+      </c>
+      <c r="E28">
+        <v>-69.84782206383423</v>
+      </c>
+      <c r="F28">
+        <v>42.249234779185</v>
+      </c>
+      <c r="G28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H28">
+        <v>50.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>34.61</v>
+      </c>
+      <c r="K28">
+        <v>12.5</v>
+      </c>
+      <c r="L28">
+        <v>22.11</v>
+      </c>
+      <c r="M28">
+        <v>1.99838880505545</v>
+      </c>
+      <c r="N28">
+        <v>20.11161119494455</v>
+      </c>
+      <c r="O28">
+        <v>4.993494361223135</v>
+      </c>
+      <c r="P28">
+        <v>15.11811683372141</v>
+      </c>
+      <c r="Q28">
+        <v>27.61811683372141</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1039152674357033</v>
+      </c>
+      <c r="T28">
+        <v>0.8774319031899014</v>
+      </c>
+      <c r="U28">
+        <v>0.0473</v>
+      </c>
+      <c r="V28">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W28">
+        <v>0.03555592435153948</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>11.06391306039492</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08598150232904404</v>
+      </c>
+      <c r="C29">
+        <v>122.2878726167227</v>
+      </c>
+      <c r="D29">
+        <v>157.9620779643379</v>
+      </c>
+      <c r="E29">
+        <v>-68.22285149540403</v>
+      </c>
+      <c r="F29">
+        <v>43.87420534761519</v>
+      </c>
+      <c r="G29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H29">
+        <v>50.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>34.61</v>
+      </c>
+      <c r="K29">
+        <v>12.5</v>
+      </c>
+      <c r="L29">
+        <v>22.11</v>
+      </c>
+      <c r="M29">
+        <v>2.075249912942199</v>
+      </c>
+      <c r="N29">
+        <v>20.0347500870578</v>
+      </c>
+      <c r="O29">
+        <v>4.974410583940969</v>
+      </c>
+      <c r="P29">
+        <v>15.06033950311683</v>
+      </c>
+      <c r="Q29">
+        <v>27.56033950311683</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1046320585672992</v>
+      </c>
+      <c r="T29">
+        <v>0.8870907041371108</v>
+      </c>
+      <c r="U29">
+        <v>0.0473</v>
+      </c>
+      <c r="V29">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W29">
+        <v>0.03555592435153948</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>10.65413850260252</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08582116642426733</v>
+      </c>
+      <c r="C30">
+        <v>120.8779866373092</v>
+      </c>
+      <c r="D30">
+        <v>158.1771625533546</v>
+      </c>
+      <c r="E30">
+        <v>-66.59788092697383</v>
+      </c>
+      <c r="F30">
+        <v>45.49917591604538</v>
+      </c>
+      <c r="G30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H30">
+        <v>50.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>34.61</v>
+      </c>
+      <c r="K30">
+        <v>12.5</v>
+      </c>
+      <c r="L30">
+        <v>22.11</v>
+      </c>
+      <c r="M30">
+        <v>2.152111020828947</v>
+      </c>
+      <c r="N30">
+        <v>19.95788897917105</v>
+      </c>
+      <c r="O30">
+        <v>4.955326806658803</v>
+      </c>
+      <c r="P30">
+        <v>15.00256217251225</v>
+      </c>
+      <c r="Q30">
+        <v>27.50256217251225</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1053687605636615</v>
+      </c>
+      <c r="T30">
+        <v>0.8970178051106313</v>
+      </c>
+      <c r="U30">
+        <v>0.0473</v>
+      </c>
+      <c r="V30">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W30">
+        <v>0.03555592435153948</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>10.273633556081</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08648921590290283</v>
+      </c>
+      <c r="C31">
+        <v>118.3606949592784</v>
+      </c>
+      <c r="D31">
+        <v>157.2848414437539</v>
+      </c>
+      <c r="E31">
+        <v>-64.97291035854366</v>
+      </c>
+      <c r="F31">
+        <v>47.12414648447557</v>
+      </c>
+      <c r="G31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H31">
+        <v>50.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>34.61</v>
+      </c>
+      <c r="K31">
+        <v>12.5</v>
+      </c>
+      <c r="L31">
+        <v>22.11</v>
+      </c>
+      <c r="M31">
+        <v>2.408043885356701</v>
+      </c>
+      <c r="N31">
+        <v>19.7019561146433</v>
+      </c>
+      <c r="O31">
+        <v>4.891781459471887</v>
+      </c>
+      <c r="P31">
+        <v>14.81017465517141</v>
+      </c>
+      <c r="Q31">
+        <v>27.31017465517141</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1061262147289355</v>
+      </c>
+      <c r="T31">
+        <v>0.9072245427312935</v>
+      </c>
+      <c r="U31">
+        <v>0.0511</v>
+      </c>
+      <c r="V31">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W31">
+        <v>0.03841242567365047</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>9.18172635243517</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08635744501134725</v>
+      </c>
+      <c r="C32">
+        <v>116.9109342861648</v>
+      </c>
+      <c r="D32">
+        <v>157.4600513390706</v>
+      </c>
+      <c r="E32">
+        <v>-63.34793979011346</v>
+      </c>
+      <c r="F32">
+        <v>48.74911705290576</v>
+      </c>
+      <c r="G32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H32">
+        <v>50.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>34.61</v>
+      </c>
+      <c r="K32">
+        <v>12.5</v>
+      </c>
+      <c r="L32">
+        <v>22.11</v>
+      </c>
+      <c r="M32">
+        <v>2.491079881403484</v>
+      </c>
+      <c r="N32">
+        <v>19.61892011859651</v>
+      </c>
+      <c r="O32">
+        <v>4.871164524606797</v>
+      </c>
+      <c r="P32">
+        <v>14.74775559398972</v>
+      </c>
+      <c r="Q32">
+        <v>27.24775559398972</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1069053104417887</v>
+      </c>
+      <c r="T32">
+        <v>0.9177229014268317</v>
+      </c>
+      <c r="U32">
+        <v>0.0511</v>
+      </c>
+      <c r="V32">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W32">
+        <v>0.03841242567365047</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.875668807353996</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08622567411979166</v>
+      </c>
+      <c r="C33">
+        <v>115.4615644039545</v>
+      </c>
+      <c r="D33">
+        <v>157.6356520252905</v>
+      </c>
+      <c r="E33">
+        <v>-61.72296922168326</v>
+      </c>
+      <c r="F33">
+        <v>50.37408762133595</v>
+      </c>
+      <c r="G33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H33">
+        <v>50.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>34.61</v>
+      </c>
+      <c r="K33">
+        <v>12.5</v>
+      </c>
+      <c r="L33">
+        <v>22.11</v>
+      </c>
+      <c r="M33">
+        <v>2.574115877450267</v>
+      </c>
+      <c r="N33">
+        <v>19.53588412254973</v>
+      </c>
+      <c r="O33">
+        <v>4.850547589741709</v>
+      </c>
+      <c r="P33">
+        <v>14.68533653280802</v>
+      </c>
+      <c r="Q33">
+        <v>27.18533653280802</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1077069886390725</v>
+      </c>
+      <c r="T33">
+        <v>0.9285255603744144</v>
+      </c>
+      <c r="U33">
+        <v>0.0511</v>
+      </c>
+      <c r="V33">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W33">
+        <v>0.03841242567365047</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.589356910342577</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08609390322823607</v>
+      </c>
+      <c r="C34">
+        <v>114.0125866215465</v>
+      </c>
+      <c r="D34">
+        <v>157.8116448113127</v>
+      </c>
+      <c r="E34">
+        <v>-60.09799865325307</v>
+      </c>
+      <c r="F34">
+        <v>51.99905818976615</v>
+      </c>
+      <c r="G34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H34">
+        <v>50.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>34.61</v>
+      </c>
+      <c r="K34">
+        <v>12.5</v>
+      </c>
+      <c r="L34">
+        <v>22.11</v>
+      </c>
+      <c r="M34">
+        <v>2.65715187349705</v>
+      </c>
+      <c r="N34">
+        <v>19.45284812650295</v>
+      </c>
+      <c r="O34">
+        <v>4.829930654876621</v>
+      </c>
+      <c r="P34">
+        <v>14.62291747162633</v>
+      </c>
+      <c r="Q34">
+        <v>27.12291747162633</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1085322456068646</v>
+      </c>
+      <c r="T34">
+        <v>0.9396459445851613</v>
+      </c>
+      <c r="U34">
+        <v>0.0511</v>
+      </c>
+      <c r="V34">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W34">
+        <v>0.03841242567365047</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>8.320939506894373</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08596213233668049</v>
+      </c>
+      <c r="C35">
+        <v>112.5640022536915</v>
+      </c>
+      <c r="D35">
+        <v>157.9880310118879</v>
+      </c>
+      <c r="E35">
+        <v>-58.47302808482288</v>
+      </c>
+      <c r="F35">
+        <v>53.62402875819634</v>
+      </c>
+      <c r="G35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H35">
+        <v>50.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>34.61</v>
+      </c>
+      <c r="K35">
+        <v>12.5</v>
+      </c>
+      <c r="L35">
+        <v>22.11</v>
+      </c>
+      <c r="M35">
+        <v>2.740187869543833</v>
+      </c>
+      <c r="N35">
+        <v>19.36981213045617</v>
+      </c>
+      <c r="O35">
+        <v>4.809313720011533</v>
+      </c>
+      <c r="P35">
+        <v>14.56049841044464</v>
+      </c>
+      <c r="Q35">
+        <v>27.06049841044464</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1093821371110087</v>
+      </c>
+      <c r="T35">
+        <v>0.9510982805633933</v>
+      </c>
+      <c r="U35">
+        <v>0.0511</v>
+      </c>
+      <c r="V35">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W35">
+        <v>0.03841242567365047</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>8.06878982486727</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.0858303614451249</v>
+      </c>
+      <c r="C36">
+        <v>111.115812621025</v>
+      </c>
+      <c r="D36">
+        <v>158.1648119476515</v>
+      </c>
+      <c r="E36">
+        <v>-56.84805751639269</v>
+      </c>
+      <c r="F36">
+        <v>55.24899932662653</v>
+      </c>
+      <c r="G36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H36">
+        <v>50.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>34.61</v>
+      </c>
+      <c r="K36">
+        <v>12.5</v>
+      </c>
+      <c r="L36">
+        <v>22.11</v>
+      </c>
+      <c r="M36">
+        <v>2.823223865590616</v>
+      </c>
+      <c r="N36">
+        <v>19.28677613440938</v>
+      </c>
+      <c r="O36">
+        <v>4.788696785146444</v>
+      </c>
+      <c r="P36">
+        <v>14.49807934926294</v>
+      </c>
+      <c r="Q36">
+        <v>26.99807934926294</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1102577829031572</v>
+      </c>
+      <c r="T36">
+        <v>0.9628976570258141</v>
+      </c>
+      <c r="U36">
+        <v>0.0511</v>
+      </c>
+      <c r="V36">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W36">
+        <v>0.03841242567365047</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.831472477077055</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08619847828493875</v>
+      </c>
+      <c r="C37">
+        <v>108.9979726467216</v>
+      </c>
+      <c r="D37">
+        <v>157.6719425417783</v>
+      </c>
+      <c r="E37">
+        <v>-55.22308694796249</v>
+      </c>
+      <c r="F37">
+        <v>56.87396989505673</v>
+      </c>
+      <c r="G37">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H37">
+        <v>50.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>34.61</v>
+      </c>
+      <c r="K37">
+        <v>12.5</v>
+      </c>
+      <c r="L37">
+        <v>22.11</v>
+      </c>
+      <c r="M37">
+        <v>3.014320404438007</v>
+      </c>
+      <c r="N37">
+        <v>19.09567959556199</v>
+      </c>
+      <c r="O37">
+        <v>4.741249592580213</v>
+      </c>
+      <c r="P37">
+        <v>14.35443000298178</v>
+      </c>
+      <c r="Q37">
+        <v>26.85443000298178</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1111603716427564</v>
+      </c>
+      <c r="T37">
+        <v>0.9750600912255402</v>
+      </c>
+      <c r="U37">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W37">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>7.334986674756697</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08608098989999373</v>
+      </c>
+      <c r="C38">
+        <v>107.5299724929675</v>
+      </c>
+      <c r="D38">
+        <v>157.8289129564544</v>
+      </c>
+      <c r="E38">
+        <v>-53.59811637953231</v>
+      </c>
+      <c r="F38">
+        <v>58.49894046348691</v>
+      </c>
+      <c r="G38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H38">
+        <v>50.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>34.61</v>
+      </c>
+      <c r="K38">
+        <v>12.5</v>
+      </c>
+      <c r="L38">
+        <v>22.11</v>
+      </c>
+      <c r="M38">
+        <v>3.100443844564806</v>
+      </c>
+      <c r="N38">
+        <v>19.00955615543519</v>
+      </c>
+      <c r="O38">
+        <v>4.719866078923663</v>
+      </c>
+      <c r="P38">
+        <v>14.28969007651153</v>
+      </c>
+      <c r="Q38">
+        <v>26.78969007651153</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1120911662804681</v>
+      </c>
+      <c r="T38">
+        <v>0.9876026014940075</v>
+      </c>
+      <c r="U38">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W38">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>7.131237044902346</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08596350151504868</v>
+      </c>
+      <c r="C39">
+        <v>106.0622851946931</v>
+      </c>
+      <c r="D39">
+        <v>157.9861962266102</v>
+      </c>
+      <c r="E39">
+        <v>-51.97314581110211</v>
+      </c>
+      <c r="F39">
+        <v>60.1239110319171</v>
+      </c>
+      <c r="G39">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H39">
+        <v>50.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>34.61</v>
+      </c>
+      <c r="K39">
+        <v>12.5</v>
+      </c>
+      <c r="L39">
+        <v>22.11</v>
+      </c>
+      <c r="M39">
+        <v>3.186567284691607</v>
+      </c>
+      <c r="N39">
+        <v>18.92343271530839</v>
+      </c>
+      <c r="O39">
+        <v>4.698482565267114</v>
+      </c>
+      <c r="P39">
+        <v>14.22495015004128</v>
+      </c>
+      <c r="Q39">
+        <v>26.72495015004128</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1130515099542976</v>
+      </c>
+      <c r="T39">
+        <v>1.000543286691633</v>
+      </c>
+      <c r="U39">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W39">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.938500908553634</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08584601313010366</v>
+      </c>
+      <c r="C40">
+        <v>104.5949116881531</v>
+      </c>
+      <c r="D40">
+        <v>158.1437932885005</v>
+      </c>
+      <c r="E40">
+        <v>-50.34817524267191</v>
+      </c>
+      <c r="F40">
+        <v>61.7488816003473</v>
+      </c>
+      <c r="G40">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H40">
+        <v>50.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>34.61</v>
+      </c>
+      <c r="K40">
+        <v>12.5</v>
+      </c>
+      <c r="L40">
+        <v>22.11</v>
+      </c>
+      <c r="M40">
+        <v>3.272690724818407</v>
+      </c>
+      <c r="N40">
+        <v>18.83730927518159</v>
+      </c>
+      <c r="O40">
+        <v>4.677099051610564</v>
+      </c>
+      <c r="P40">
+        <v>14.16021022357103</v>
+      </c>
+      <c r="Q40">
+        <v>26.66021022357103</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1140428324563151</v>
+      </c>
+      <c r="T40">
+        <v>1.013901413347246</v>
+      </c>
+      <c r="U40">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W40">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.755908779381169</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08572852474515863</v>
+      </c>
+      <c r="C41">
+        <v>103.1278529133417</v>
+      </c>
+      <c r="D41">
+        <v>158.3017050821192</v>
+      </c>
+      <c r="E41">
+        <v>-48.72320467424172</v>
+      </c>
+      <c r="F41">
+        <v>63.3738521687775</v>
+      </c>
+      <c r="G41">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H41">
+        <v>50.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>34.61</v>
+      </c>
+      <c r="K41">
+        <v>12.5</v>
+      </c>
+      <c r="L41">
+        <v>22.11</v>
+      </c>
+      <c r="M41">
+        <v>3.358814164945207</v>
+      </c>
+      <c r="N41">
+        <v>18.75118583505479</v>
+      </c>
+      <c r="O41">
+        <v>4.655715537954014</v>
+      </c>
+      <c r="P41">
+        <v>14.09547029710078</v>
+      </c>
+      <c r="Q41">
+        <v>26.59547029710078</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.115066657335448</v>
+      </c>
+      <c r="T41">
+        <v>1.027697511368617</v>
+      </c>
+      <c r="U41">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W41">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.582680349140626</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.0856110363602136</v>
+      </c>
+      <c r="C42">
+        <v>101.6611098140112</v>
+      </c>
+      <c r="D42">
+        <v>158.4599325512189</v>
+      </c>
+      <c r="E42">
+        <v>-47.09823410581153</v>
+      </c>
+      <c r="F42">
+        <v>64.99882273720769</v>
+      </c>
+      <c r="G42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H42">
+        <v>50.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>34.61</v>
+      </c>
+      <c r="K42">
+        <v>12.5</v>
+      </c>
+      <c r="L42">
+        <v>22.11</v>
+      </c>
+      <c r="M42">
+        <v>3.444937605072008</v>
+      </c>
+      <c r="N42">
+        <v>18.66506239492799</v>
+      </c>
+      <c r="O42">
+        <v>4.634332024297465</v>
+      </c>
+      <c r="P42">
+        <v>14.03073037063053</v>
+      </c>
+      <c r="Q42">
+        <v>26.53073037063053</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.116124609710552</v>
+      </c>
+      <c r="T42">
+        <v>1.041953479324033</v>
+      </c>
+      <c r="U42">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W42">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>6.418113340412111</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08549354797526856</v>
+      </c>
+      <c r="C43">
+        <v>100.1946833376912</v>
+      </c>
+      <c r="D43">
+        <v>158.6184766433291</v>
+      </c>
+      <c r="E43">
+        <v>-45.47326353738134</v>
+      </c>
+      <c r="F43">
+        <v>66.62379330563788</v>
+      </c>
+      <c r="G43">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H43">
+        <v>50.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>34.61</v>
+      </c>
+      <c r="K43">
+        <v>12.5</v>
+      </c>
+      <c r="L43">
+        <v>22.11</v>
+      </c>
+      <c r="M43">
+        <v>3.531061045198808</v>
+      </c>
+      <c r="N43">
+        <v>18.57893895480119</v>
+      </c>
+      <c r="O43">
+        <v>4.612948510640915</v>
+      </c>
+      <c r="P43">
+        <v>13.96599044416028</v>
+      </c>
+      <c r="Q43">
+        <v>26.46599044416028</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1172184248780324</v>
+      </c>
+      <c r="T43">
+        <v>1.056692700430481</v>
+      </c>
+      <c r="U43">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W43">
+        <v>0.03984067633470597</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>6.261573990645962</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08600749672468493</v>
+      </c>
+      <c r="C44">
+        <v>97.87849867668876</v>
+      </c>
+      <c r="D44">
+        <v>157.9272625507568</v>
+      </c>
+      <c r="E44">
+        <v>-43.84829296895116</v>
+      </c>
+      <c r="F44">
+        <v>68.24876387406806</v>
+      </c>
+      <c r="G44">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H44">
+        <v>50.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>34.61</v>
+      </c>
+      <c r="K44">
+        <v>12.5</v>
+      </c>
+      <c r="L44">
+        <v>22.11</v>
+      </c>
+      <c r="M44">
+        <v>3.753682013073743</v>
+      </c>
+      <c r="N44">
+        <v>18.35631798692626</v>
+      </c>
+      <c r="O44">
+        <v>4.557674145151343</v>
+      </c>
+      <c r="P44">
+        <v>13.79864384177491</v>
+      </c>
+      <c r="Q44">
+        <v>26.29864384177491</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1183499578099087</v>
+      </c>
+      <c r="T44">
+        <v>1.071940170540599</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W44">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.890216572153108</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.0859050425572247</v>
+      </c>
+      <c r="C45">
+        <v>96.3908384242022</v>
+      </c>
+      <c r="D45">
+        <v>158.0645728667005</v>
+      </c>
+      <c r="E45">
+        <v>-42.22332240052096</v>
+      </c>
+      <c r="F45">
+        <v>69.87373444249826</v>
+      </c>
+      <c r="G45">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H45">
+        <v>50.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>34.61</v>
+      </c>
+      <c r="K45">
+        <v>12.5</v>
+      </c>
+      <c r="L45">
+        <v>22.11</v>
+      </c>
+      <c r="M45">
+        <v>3.843055394337404</v>
+      </c>
+      <c r="N45">
+        <v>18.26694460566259</v>
+      </c>
+      <c r="O45">
+        <v>4.535483706451149</v>
+      </c>
+      <c r="P45">
+        <v>13.73146089921145</v>
+      </c>
+      <c r="Q45">
+        <v>26.23146089921145</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1195211936516754</v>
+      </c>
+      <c r="T45">
+        <v>1.087722639601949</v>
+      </c>
+      <c r="U45">
+        <v>0.055</v>
+      </c>
+      <c r="V45">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W45">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.75323479140536</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08580258838976446</v>
+      </c>
+      <c r="C46">
+        <v>94.90341714919931</v>
+      </c>
+      <c r="D46">
+        <v>158.2021221601278</v>
+      </c>
+      <c r="E46">
+        <v>-40.59835183209077</v>
+      </c>
+      <c r="F46">
+        <v>71.49870501092845</v>
+      </c>
+      <c r="G46">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H46">
+        <v>50.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>34.61</v>
+      </c>
+      <c r="K46">
+        <v>12.5</v>
+      </c>
+      <c r="L46">
+        <v>22.11</v>
+      </c>
+      <c r="M46">
+        <v>3.932428775601065</v>
+      </c>
+      <c r="N46">
+        <v>18.17757122439894</v>
+      </c>
+      <c r="O46">
+        <v>4.513293267750957</v>
+      </c>
+      <c r="P46">
+        <v>13.66427795664798</v>
+      </c>
+      <c r="Q46">
+        <v>26.16427795664798</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1207342593449337</v>
+      </c>
+      <c r="T46">
+        <v>1.104068768272634</v>
+      </c>
+      <c r="U46">
+        <v>0.055</v>
+      </c>
+      <c r="V46">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W46">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.622479455237057</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08570013422230423</v>
+      </c>
+      <c r="C47">
+        <v>93.41623547610486</v>
+      </c>
+      <c r="D47">
+        <v>158.3399110554635</v>
+      </c>
+      <c r="E47">
+        <v>-38.97338126366057</v>
+      </c>
+      <c r="F47">
+        <v>73.12367557935865</v>
+      </c>
+      <c r="G47">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H47">
+        <v>50.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>34.61</v>
+      </c>
+      <c r="K47">
+        <v>12.5</v>
+      </c>
+      <c r="L47">
+        <v>22.11</v>
+      </c>
+      <c r="M47">
+        <v>4.021802156864726</v>
+      </c>
+      <c r="N47">
+        <v>18.08819784313527</v>
+      </c>
+      <c r="O47">
+        <v>4.491102829050763</v>
+      </c>
+      <c r="P47">
+        <v>13.59709501408451</v>
+      </c>
+      <c r="Q47">
+        <v>26.09709501408451</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1219914365179469</v>
+      </c>
+      <c r="T47">
+        <v>1.121009301622252</v>
+      </c>
+      <c r="U47">
+        <v>0.055</v>
+      </c>
+      <c r="V47">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W47">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.497535467342899</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.085597680054844</v>
+      </c>
+      <c r="C48">
+        <v>91.92929403152095</v>
+      </c>
+      <c r="D48">
+        <v>158.4779401793098</v>
+      </c>
+      <c r="E48">
+        <v>-37.34841069523038</v>
+      </c>
+      <c r="F48">
+        <v>74.74864614778883</v>
+      </c>
+      <c r="G48">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H48">
+        <v>50.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>34.61</v>
+      </c>
+      <c r="K48">
+        <v>12.5</v>
+      </c>
+      <c r="L48">
+        <v>22.11</v>
+      </c>
+      <c r="M48">
+        <v>4.111175538128386</v>
+      </c>
+      <c r="N48">
+        <v>17.99882446187161</v>
+      </c>
+      <c r="O48">
+        <v>4.46891239035057</v>
+      </c>
+      <c r="P48">
+        <v>13.52991207152104</v>
+      </c>
+      <c r="Q48">
+        <v>26.02991207152104</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.123295175808479</v>
+      </c>
+      <c r="T48">
+        <v>1.138577262132968</v>
+      </c>
+      <c r="U48">
+        <v>0.055</v>
+      </c>
+      <c r="V48">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W48">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.378023826748489</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08549522588738376</v>
+      </c>
+      <c r="C49">
+        <v>90.44259344423662</v>
+      </c>
+      <c r="D49">
+        <v>158.6162101604557</v>
+      </c>
+      <c r="E49">
+        <v>-35.72344012680018</v>
+      </c>
+      <c r="F49">
+        <v>76.37361671621903</v>
+      </c>
+      <c r="G49">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H49">
+        <v>50.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>34.61</v>
+      </c>
+      <c r="K49">
+        <v>12.5</v>
+      </c>
+      <c r="L49">
+        <v>22.11</v>
+      </c>
+      <c r="M49">
+        <v>4.200548919392046</v>
+      </c>
+      <c r="N49">
+        <v>17.90945108060795</v>
+      </c>
+      <c r="O49">
+        <v>4.446721951650376</v>
+      </c>
+      <c r="P49">
+        <v>13.46272912895757</v>
+      </c>
+      <c r="Q49">
+        <v>25.96272912895758</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1246481128080879</v>
+      </c>
+      <c r="T49">
+        <v>1.156808164549748</v>
+      </c>
+      <c r="U49">
+        <v>0.055</v>
+      </c>
+      <c r="V49">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W49">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.263597787881499</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08539277171992352</v>
+      </c>
+      <c r="C50">
+        <v>88.95613434523706</v>
+      </c>
+      <c r="D50">
+        <v>158.7547216298863</v>
+      </c>
+      <c r="E50">
+        <v>-34.09846955837</v>
+      </c>
+      <c r="F50">
+        <v>77.99858728464922</v>
+      </c>
+      <c r="G50">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H50">
+        <v>50.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>34.61</v>
+      </c>
+      <c r="K50">
+        <v>12.5</v>
+      </c>
+      <c r="L50">
+        <v>22.11</v>
+      </c>
+      <c r="M50">
+        <v>4.289922300655707</v>
+      </c>
+      <c r="N50">
+        <v>17.82007769934429</v>
+      </c>
+      <c r="O50">
+        <v>4.424531512950185</v>
+      </c>
+      <c r="P50">
+        <v>13.39554618639411</v>
+      </c>
+      <c r="Q50">
+        <v>25.89554618639411</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1260530858461433</v>
+      </c>
+      <c r="T50">
+        <v>1.175740255521019</v>
+      </c>
+      <c r="U50">
+        <v>0.055</v>
+      </c>
+      <c r="V50">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W50">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.153939500633968</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.0852903175524633</v>
+      </c>
+      <c r="C51">
+        <v>87.46991736771352</v>
+      </c>
+      <c r="D51">
+        <v>158.8934752207929</v>
+      </c>
+      <c r="E51">
+        <v>-32.47349898993981</v>
+      </c>
+      <c r="F51">
+        <v>79.6235578530794</v>
+      </c>
+      <c r="G51">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H51">
+        <v>50.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>34.61</v>
+      </c>
+      <c r="K51">
+        <v>12.5</v>
+      </c>
+      <c r="L51">
+        <v>22.11</v>
+      </c>
+      <c r="M51">
+        <v>4.379295681919367</v>
+      </c>
+      <c r="N51">
+        <v>17.73070431808063</v>
+      </c>
+      <c r="O51">
+        <v>4.402341074249992</v>
+      </c>
+      <c r="P51">
+        <v>13.32836324383064</v>
+      </c>
+      <c r="Q51">
+        <v>25.82836324383064</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1275131558660832</v>
+      </c>
+      <c r="T51">
+        <v>1.195414781432341</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W51">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.048757061845521</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08518786338500306</v>
+      </c>
+      <c r="C52">
+        <v>85.98394314707292</v>
+      </c>
+      <c r="D52">
+        <v>159.0324715685825</v>
+      </c>
+      <c r="E52">
+        <v>-30.84852842150961</v>
+      </c>
+      <c r="F52">
+        <v>81.2485284215096</v>
+      </c>
+      <c r="G52">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H52">
+        <v>50.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>34.61</v>
+      </c>
+      <c r="K52">
+        <v>12.5</v>
+      </c>
+      <c r="L52">
+        <v>22.11</v>
+      </c>
+      <c r="M52">
+        <v>4.468669063183028</v>
+      </c>
+      <c r="N52">
+        <v>17.64133093681697</v>
+      </c>
+      <c r="O52">
+        <v>4.380150635549798</v>
+      </c>
+      <c r="P52">
+        <v>13.26118030126717</v>
+      </c>
+      <c r="Q52">
+        <v>25.76118030126717</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1290316286868207</v>
+      </c>
+      <c r="T52">
+        <v>1.215876288380116</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W52">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.94778192060861</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08508540921754282</v>
+      </c>
+      <c r="C53">
+        <v>84.49821232094735</v>
+      </c>
+      <c r="D53">
+        <v>159.1717113108872</v>
+      </c>
+      <c r="E53">
+        <v>-29.22355785307941</v>
+      </c>
+      <c r="F53">
+        <v>82.8734989899398</v>
+      </c>
+      <c r="G53">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H53">
+        <v>50.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>34.61</v>
+      </c>
+      <c r="K53">
+        <v>12.5</v>
+      </c>
+      <c r="L53">
+        <v>22.11</v>
+      </c>
+      <c r="M53">
+        <v>4.55804244444669</v>
+      </c>
+      <c r="N53">
+        <v>17.55195755555331</v>
+      </c>
+      <c r="O53">
+        <v>4.357960196849604</v>
+      </c>
+      <c r="P53">
+        <v>13.1939973587037</v>
+      </c>
+      <c r="Q53">
+        <v>25.6939973587037</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1306120799900372</v>
+      </c>
+      <c r="T53">
+        <v>1.237172958876779</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W53">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.850766588831969</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08498295505008258</v>
+      </c>
+      <c r="C54">
+        <v>83.01272552920405</v>
+      </c>
+      <c r="D54">
+        <v>159.311195087574</v>
+      </c>
+      <c r="E54">
+        <v>-27.59858728464923</v>
+      </c>
+      <c r="F54">
+        <v>84.49846955836999</v>
+      </c>
+      <c r="G54">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H54">
+        <v>50.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>34.61</v>
+      </c>
+      <c r="K54">
+        <v>12.5</v>
+      </c>
+      <c r="L54">
+        <v>22.11</v>
+      </c>
+      <c r="M54">
+        <v>4.64741582571035</v>
+      </c>
+      <c r="N54">
+        <v>17.46258417428965</v>
+      </c>
+      <c r="O54">
+        <v>4.335769758149412</v>
+      </c>
+      <c r="P54">
+        <v>13.12681441614024</v>
+      </c>
+      <c r="Q54">
+        <v>25.62681441614024</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1322583834308878</v>
+      </c>
+      <c r="T54">
+        <v>1.259356990644136</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W54">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.757482615969817</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08488050088262236</v>
+      </c>
+      <c r="C55">
+        <v>81.52748341395507</v>
+      </c>
+      <c r="D55">
+        <v>159.4509235407553</v>
+      </c>
+      <c r="E55">
+        <v>-25.97361671621903</v>
+      </c>
+      <c r="F55">
+        <v>86.12344012680019</v>
+      </c>
+      <c r="G55">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H55">
+        <v>50.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>34.61</v>
+      </c>
+      <c r="K55">
+        <v>12.5</v>
+      </c>
+      <c r="L55">
+        <v>22.11</v>
+      </c>
+      <c r="M55">
+        <v>4.73678920697401</v>
+      </c>
+      <c r="N55">
+        <v>17.37321079302599</v>
+      </c>
+      <c r="O55">
+        <v>4.313579319449219</v>
+      </c>
+      <c r="P55">
+        <v>13.05963147357677</v>
+      </c>
+      <c r="Q55">
+        <v>25.55963147357677</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1339747423373066</v>
+      </c>
+      <c r="T55">
+        <v>1.282485023763296</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W55">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.667718793026991</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08477804671516211</v>
+      </c>
+      <c r="C56">
+        <v>80.0424866195672</v>
+      </c>
+      <c r="D56">
+        <v>159.5908973147976</v>
+      </c>
+      <c r="E56">
+        <v>-24.34864614778884</v>
+      </c>
+      <c r="F56">
+        <v>87.74841069523038</v>
+      </c>
+      <c r="G56">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H56">
+        <v>50.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>34.61</v>
+      </c>
+      <c r="K56">
+        <v>12.5</v>
+      </c>
+      <c r="L56">
+        <v>22.11</v>
+      </c>
+      <c r="M56">
+        <v>4.826162588237671</v>
+      </c>
+      <c r="N56">
+        <v>17.28383741176233</v>
+      </c>
+      <c r="O56">
+        <v>4.291388880749025</v>
+      </c>
+      <c r="P56">
+        <v>12.9924485310133</v>
+      </c>
+      <c r="Q56">
+        <v>25.4924485310133</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1357657255440043</v>
+      </c>
+      <c r="T56">
+        <v>1.306618623539811</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W56">
+        <v>0.04134409808318544</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.581279556119082</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08624666827486292</v>
+      </c>
+      <c r="C57">
+        <v>76.43426728025185</v>
+      </c>
+      <c r="D57">
+        <v>157.6076485439124</v>
+      </c>
+      <c r="E57">
+        <v>-22.72367557935864</v>
+      </c>
+      <c r="F57">
+        <v>89.37338126366058</v>
+      </c>
+      <c r="G57">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H57">
+        <v>50.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>34.61</v>
+      </c>
+      <c r="K57">
+        <v>12.5</v>
+      </c>
+      <c r="L57">
+        <v>22.11</v>
+      </c>
+      <c r="M57">
+        <v>5.255154818303242</v>
+      </c>
+      <c r="N57">
+        <v>16.85484518169676</v>
+      </c>
+      <c r="O57">
+        <v>4.184874774988098</v>
+      </c>
+      <c r="P57">
+        <v>12.66997040670866</v>
+      </c>
+      <c r="Q57">
+        <v>25.16997040670866</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1376363080043331</v>
+      </c>
+      <c r="T57">
+        <v>1.331824827750837</v>
+      </c>
+      <c r="U57">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W57">
+        <v>0.04420059940529644</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.207297551537932</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08617277912062379</v>
+      </c>
+      <c r="C58">
+        <v>74.90789940602629</v>
+      </c>
+      <c r="D58">
+        <v>157.7062512381171</v>
+      </c>
+      <c r="E58">
+        <v>-21.09870501092846</v>
+      </c>
+      <c r="F58">
+        <v>90.99835183209076</v>
+      </c>
+      <c r="G58">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H58">
+        <v>50.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>34.61</v>
+      </c>
+      <c r="K58">
+        <v>12.5</v>
+      </c>
+      <c r="L58">
+        <v>22.11</v>
+      </c>
+      <c r="M58">
+        <v>5.350703087726937</v>
+      </c>
+      <c r="N58">
+        <v>16.75929691227306</v>
+      </c>
+      <c r="O58">
+        <v>4.161151178704983</v>
+      </c>
+      <c r="P58">
+        <v>12.59814573356808</v>
+      </c>
+      <c r="Q58">
+        <v>25.09814573356808</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1395919169401313</v>
+      </c>
+      <c r="T58">
+        <v>1.35817676851691</v>
+      </c>
+      <c r="U58">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W58">
+        <v>0.04420059940529644</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.132167238117613</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08609888996638468</v>
+      </c>
+      <c r="C59">
+        <v>73.38165498491735</v>
+      </c>
+      <c r="D59">
+        <v>157.8049773854383</v>
+      </c>
+      <c r="E59">
+        <v>-19.47373444249826</v>
+      </c>
+      <c r="F59">
+        <v>92.62332240052096</v>
+      </c>
+      <c r="G59">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H59">
+        <v>50.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>34.61</v>
+      </c>
+      <c r="K59">
+        <v>12.5</v>
+      </c>
+      <c r="L59">
+        <v>22.11</v>
+      </c>
+      <c r="M59">
+        <v>5.446251357150633</v>
+      </c>
+      <c r="N59">
+        <v>16.66374864284937</v>
+      </c>
+      <c r="O59">
+        <v>4.137427582421867</v>
+      </c>
+      <c r="P59">
+        <v>12.5263210604275</v>
+      </c>
+      <c r="Q59">
+        <v>25.0263210604275</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1416384844310831</v>
+      </c>
+      <c r="T59">
+        <v>1.385754380946521</v>
+      </c>
+      <c r="U59">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W59">
+        <v>0.04420059940529644</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.059673076045374</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.08785616850179356</v>
+      </c>
+      <c r="C60">
+        <v>69.44171280560134</v>
+      </c>
+      <c r="D60">
+        <v>155.4900057745525</v>
+      </c>
+      <c r="E60">
+        <v>-17.84876387406808</v>
+      </c>
+      <c r="F60">
+        <v>94.24829296895113</v>
+      </c>
+      <c r="G60">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H60">
+        <v>50.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>34.61</v>
+      </c>
+      <c r="K60">
+        <v>12.5</v>
+      </c>
+      <c r="L60">
+        <v>22.11</v>
+      </c>
+      <c r="M60">
+        <v>5.937642457043921</v>
+      </c>
+      <c r="N60">
+        <v>16.17235754295608</v>
+      </c>
+      <c r="O60">
+        <v>4.015420515822988</v>
+      </c>
+      <c r="P60">
+        <v>12.15693702713309</v>
+      </c>
+      <c r="Q60">
+        <v>24.65693702713309</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.143782507516842</v>
+      </c>
+      <c r="T60">
+        <v>1.414645213015638</v>
+      </c>
+      <c r="U60">
+        <v>0.063</v>
+      </c>
+      <c r="V60">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W60">
+        <v>0.04735778507710332</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.72370013182093</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.0878138512042725</v>
+      </c>
+      <c r="C61">
+        <v>67.87169103826876</v>
+      </c>
+      <c r="D61">
+        <v>155.5449545756501</v>
+      </c>
+      <c r="E61">
+        <v>-16.22379330563788</v>
+      </c>
+      <c r="F61">
+        <v>95.87326353738133</v>
+      </c>
+      <c r="G61">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H61">
+        <v>50.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>34.61</v>
+      </c>
+      <c r="K61">
+        <v>12.5</v>
+      </c>
+      <c r="L61">
+        <v>22.11</v>
+      </c>
+      <c r="M61">
+        <v>6.040015602855024</v>
+      </c>
+      <c r="N61">
+        <v>16.06998439714497</v>
+      </c>
+      <c r="O61">
+        <v>3.990002376948221</v>
+      </c>
+      <c r="P61">
+        <v>12.07998202019675</v>
+      </c>
+      <c r="Q61">
+        <v>24.57998202019675</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1460311170945891</v>
+      </c>
+      <c r="T61">
+        <v>1.444945353966175</v>
+      </c>
+      <c r="U61">
+        <v>0.063</v>
+      </c>
+      <c r="V61">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W61">
+        <v>0.04735778507710332</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.660586570264643</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08777153390675144</v>
+      </c>
+      <c r="C62">
+        <v>66.30170812151212</v>
+      </c>
+      <c r="D62">
+        <v>155.5999422273237</v>
+      </c>
+      <c r="E62">
+        <v>-14.5988227372077</v>
+      </c>
+      <c r="F62">
+        <v>97.49823410581152</v>
+      </c>
+      <c r="G62">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H62">
+        <v>50.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>34.61</v>
+      </c>
+      <c r="K62">
+        <v>12.5</v>
+      </c>
+      <c r="L62">
+        <v>22.11</v>
+      </c>
+      <c r="M62">
+        <v>6.142388748666126</v>
+      </c>
+      <c r="N62">
+        <v>15.96761125133387</v>
+      </c>
+      <c r="O62">
+        <v>3.964584238073455</v>
+      </c>
+      <c r="P62">
+        <v>12.00302701326042</v>
+      </c>
+      <c r="Q62">
+        <v>24.50302701326042</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1483921571512236</v>
+      </c>
+      <c r="T62">
+        <v>1.476760501964239</v>
+      </c>
+      <c r="U62">
+        <v>0.063</v>
+      </c>
+      <c r="V62">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W62">
+        <v>0.04735778507710332</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.599576794093565</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08772921660923039</v>
+      </c>
+      <c r="C63">
+        <v>64.73176409654886</v>
+      </c>
+      <c r="D63">
+        <v>155.6549687707906</v>
+      </c>
+      <c r="E63">
+        <v>-12.9738521687775</v>
+      </c>
+      <c r="F63">
+        <v>99.12320467424172</v>
+      </c>
+      <c r="G63">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H63">
+        <v>50.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>34.61</v>
+      </c>
+      <c r="K63">
+        <v>12.5</v>
+      </c>
+      <c r="L63">
+        <v>22.11</v>
+      </c>
+      <c r="M63">
+        <v>6.244761894477229</v>
+      </c>
+      <c r="N63">
+        <v>15.86523810552277</v>
+      </c>
+      <c r="O63">
+        <v>3.939166099198688</v>
+      </c>
+      <c r="P63">
+        <v>11.92607200632408</v>
+      </c>
+      <c r="Q63">
+        <v>24.42607200632408</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1508742761851214</v>
+      </c>
+      <c r="T63">
+        <v>1.510207196013485</v>
+      </c>
+      <c r="U63">
+        <v>0.063</v>
+      </c>
+      <c r="V63">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W63">
+        <v>0.04735778507710332</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.540567338452687</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.09099593058011263</v>
+      </c>
+      <c r="C64">
+        <v>58.97039986346742</v>
+      </c>
+      <c r="D64">
+        <v>151.5185751061393</v>
+      </c>
+      <c r="E64">
+        <v>-11.34888160034731</v>
+      </c>
+      <c r="F64">
+        <v>100.7481752426719</v>
+      </c>
+      <c r="G64">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H64">
+        <v>50.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>34.61</v>
+      </c>
+      <c r="K64">
+        <v>12.5</v>
+      </c>
+      <c r="L64">
+        <v>22.11</v>
+      </c>
+      <c r="M64">
+        <v>7.0624470845113</v>
+      </c>
+      <c r="N64">
+        <v>15.0475529154887</v>
+      </c>
+      <c r="O64">
+        <v>3.736143758218012</v>
+      </c>
+      <c r="P64">
+        <v>11.31140915727069</v>
+      </c>
+      <c r="Q64">
+        <v>23.81140915727069</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1534870330629086</v>
+      </c>
+      <c r="T64">
+        <v>1.545414242381113</v>
+      </c>
+      <c r="U64">
+        <v>0.0701</v>
+      </c>
+      <c r="V64">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W64">
+        <v>0.05269493228420544</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.130642925238985</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.0910069847546626</v>
+      </c>
+      <c r="C65">
+        <v>57.33180541190093</v>
+      </c>
+      <c r="D65">
+        <v>151.504951223003</v>
+      </c>
+      <c r="E65">
+        <v>-9.723911031917112</v>
+      </c>
+      <c r="F65">
+        <v>102.3731458111021</v>
+      </c>
+      <c r="G65">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H65">
+        <v>50.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>34.61</v>
+      </c>
+      <c r="K65">
+        <v>12.5</v>
+      </c>
+      <c r="L65">
+        <v>22.11</v>
+      </c>
+      <c r="M65">
+        <v>7.176357521358257</v>
+      </c>
+      <c r="N65">
+        <v>14.93364247864174</v>
+      </c>
+      <c r="O65">
+        <v>3.707861035438311</v>
+      </c>
+      <c r="P65">
+        <v>11.22578144320343</v>
+      </c>
+      <c r="Q65">
+        <v>23.72578144320343</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1562410200421978</v>
+      </c>
+      <c r="T65">
+        <v>1.582524372336181</v>
+      </c>
+      <c r="U65">
+        <v>0.0701</v>
+      </c>
+      <c r="V65">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W65">
+        <v>0.05269493228420544</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.080950180393922</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.09101803892921256</v>
+      </c>
+      <c r="C66">
+        <v>55.69321341011337</v>
+      </c>
+      <c r="D66">
+        <v>151.4913297896457</v>
+      </c>
+      <c r="E66">
+        <v>-8.098940463486926</v>
+      </c>
+      <c r="F66">
+        <v>103.9981163795323</v>
+      </c>
+      <c r="G66">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H66">
+        <v>50.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>34.61</v>
+      </c>
+      <c r="K66">
+        <v>12.5</v>
+      </c>
+      <c r="L66">
+        <v>22.11</v>
+      </c>
+      <c r="M66">
+        <v>7.290267958205213</v>
+      </c>
+      <c r="N66">
+        <v>14.81973204179479</v>
+      </c>
+      <c r="O66">
+        <v>3.679578312658611</v>
+      </c>
+      <c r="P66">
+        <v>11.14015372913618</v>
+      </c>
+      <c r="Q66">
+        <v>23.64015372913617</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1591480062981141</v>
+      </c>
+      <c r="T66">
+        <v>1.621696176177641</v>
+      </c>
+      <c r="U66">
+        <v>0.0701</v>
+      </c>
+      <c r="V66">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W66">
+        <v>0.05269493228420544</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.032810333825267</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1014365301576117</v>
+      </c>
+      <c r="C67">
+        <v>42.23407539660721</v>
+      </c>
+      <c r="D67">
+        <v>139.6571623445697</v>
+      </c>
+      <c r="E67">
+        <v>-6.473969895056726</v>
+      </c>
+      <c r="F67">
+        <v>105.6230869479625</v>
+      </c>
+      <c r="G67">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H67">
+        <v>50.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>34.61</v>
+      </c>
+      <c r="K67">
+        <v>12.5</v>
+      </c>
+      <c r="L67">
+        <v>22.11</v>
+      </c>
+      <c r="M67">
+        <v>9.653950147043773</v>
+      </c>
+      <c r="N67">
+        <v>12.45604985295623</v>
+      </c>
+      <c r="O67">
+        <v>3.092701728416776</v>
+      </c>
+      <c r="P67">
+        <v>9.363348124539451</v>
+      </c>
+      <c r="Q67">
+        <v>21.86334812453945</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1622211060543686</v>
+      </c>
+      <c r="T67">
+        <v>1.663106368810041</v>
+      </c>
+      <c r="U67">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W67">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.290254213377154</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1016076987483747</v>
+      </c>
+      <c r="C68">
+        <v>40.43009562270719</v>
+      </c>
+      <c r="D68">
+        <v>139.4781531390999</v>
+      </c>
+      <c r="E68">
+        <v>-4.84899932662654</v>
+      </c>
+      <c r="F68">
+        <v>107.2480575163927</v>
+      </c>
+      <c r="G68">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H68">
+        <v>50.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>34.61</v>
+      </c>
+      <c r="K68">
+        <v>12.5</v>
+      </c>
+      <c r="L68">
+        <v>22.11</v>
+      </c>
+      <c r="M68">
+        <v>9.802472456998292</v>
+      </c>
+      <c r="N68">
+        <v>12.30752754300171</v>
+      </c>
+      <c r="O68">
+        <v>3.055825253922273</v>
+      </c>
+      <c r="P68">
+        <v>9.251702289079436</v>
+      </c>
+      <c r="Q68">
+        <v>21.75170228907944</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1654749763845203</v>
+      </c>
+      <c r="T68">
+        <v>1.706952455126701</v>
+      </c>
+      <c r="U68">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W68">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.255553391962349</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1017788673391377</v>
+      </c>
+      <c r="C69">
+        <v>38.62657416077728</v>
+      </c>
+      <c r="D69">
+        <v>139.2996022456002</v>
+      </c>
+      <c r="E69">
+        <v>-3.22402875819634</v>
+      </c>
+      <c r="F69">
+        <v>108.8730280848229</v>
+      </c>
+      <c r="G69">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H69">
+        <v>50.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>34.61</v>
+      </c>
+      <c r="K69">
+        <v>12.5</v>
+      </c>
+      <c r="L69">
+        <v>22.11</v>
+      </c>
+      <c r="M69">
+        <v>9.950994766952812</v>
+      </c>
+      <c r="N69">
+        <v>12.15900523304719</v>
+      </c>
+      <c r="O69">
+        <v>3.01894877942777</v>
+      </c>
+      <c r="P69">
+        <v>9.140056453619417</v>
+      </c>
+      <c r="Q69">
+        <v>21.64005645361942</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1689260509771056</v>
+      </c>
+      <c r="T69">
+        <v>1.753455880008006</v>
+      </c>
+      <c r="U69">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W69">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.221888415962911</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1019500359299008</v>
+      </c>
+      <c r="C70">
+        <v>36.82350925296404</v>
+      </c>
+      <c r="D70">
+        <v>139.1215079062171</v>
+      </c>
+      <c r="E70">
+        <v>-1.599058189766154</v>
+      </c>
+      <c r="F70">
+        <v>110.4979986532531</v>
+      </c>
+      <c r="G70">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H70">
+        <v>50.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>34.61</v>
+      </c>
+      <c r="K70">
+        <v>12.5</v>
+      </c>
+      <c r="L70">
+        <v>22.11</v>
+      </c>
+      <c r="M70">
+        <v>10.09951707690733</v>
+      </c>
+      <c r="N70">
+        <v>12.01048292309267</v>
+      </c>
+      <c r="O70">
+        <v>2.982072304933268</v>
+      </c>
+      <c r="P70">
+        <v>9.028410618159402</v>
+      </c>
+      <c r="Q70">
+        <v>21.5284106181594</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1725928177317273</v>
+      </c>
+      <c r="T70">
+        <v>1.802865768944393</v>
+      </c>
+      <c r="U70">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W70">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.189213586316398</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1021212045206638</v>
+      </c>
+      <c r="C71">
+        <v>35.02089915039198</v>
+      </c>
+      <c r="D71">
+        <v>138.9438683720753</v>
+      </c>
+      <c r="E71">
+        <v>0.02591237866404583</v>
+      </c>
+      <c r="F71">
+        <v>112.1229692216833</v>
+      </c>
+      <c r="G71">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H71">
+        <v>50.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>34.61</v>
+      </c>
+      <c r="K71">
+        <v>12.5</v>
+      </c>
+      <c r="L71">
+        <v>22.11</v>
+      </c>
+      <c r="M71">
+        <v>10.24803938686185</v>
+      </c>
+      <c r="N71">
+        <v>11.86196061313815</v>
+      </c>
+      <c r="O71">
+        <v>2.945195830438765</v>
+      </c>
+      <c r="P71">
+        <v>8.916764782699383</v>
+      </c>
+      <c r="Q71">
+        <v>21.41676478269938</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1764961500834215</v>
+      </c>
+      <c r="T71">
+        <v>1.85546339265087</v>
+      </c>
+      <c r="U71">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W71">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.157485853181377</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1022923731114268</v>
+      </c>
+      <c r="C72">
+        <v>33.21874211310669</v>
+      </c>
+      <c r="D72">
+        <v>138.7666819032202</v>
+      </c>
+      <c r="E72">
+        <v>1.650882947094246</v>
+      </c>
+      <c r="F72">
+        <v>113.7479397901135</v>
+      </c>
+      <c r="G72">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H72">
+        <v>50.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>34.61</v>
+      </c>
+      <c r="K72">
+        <v>12.5</v>
+      </c>
+      <c r="L72">
+        <v>22.11</v>
+      </c>
+      <c r="M72">
+        <v>10.39656169681637</v>
+      </c>
+      <c r="N72">
+        <v>11.71343830318363</v>
+      </c>
+      <c r="O72">
+        <v>2.908319355944262</v>
+      </c>
+      <c r="P72">
+        <v>8.805118947239366</v>
+      </c>
+      <c r="Q72">
+        <v>21.30511894723936</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1806597045918952</v>
+      </c>
+      <c r="T72">
+        <v>1.911567524604445</v>
+      </c>
+      <c r="U72">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W72">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.126664626707357</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1024635417021899</v>
+      </c>
+      <c r="C73">
+        <v>31.41703641001786</v>
+      </c>
+      <c r="D73">
+        <v>138.5899467685615</v>
+      </c>
+      <c r="E73">
+        <v>3.275853515524418</v>
+      </c>
+      <c r="F73">
+        <v>115.3729103585436</v>
+      </c>
+      <c r="G73">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H73">
+        <v>50.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>34.61</v>
+      </c>
+      <c r="K73">
+        <v>12.5</v>
+      </c>
+      <c r="L73">
+        <v>22.11</v>
+      </c>
+      <c r="M73">
+        <v>10.54508400677089</v>
+      </c>
+      <c r="N73">
+        <v>11.56491599322911</v>
+      </c>
+      <c r="O73">
+        <v>2.871442881449759</v>
+      </c>
+      <c r="P73">
+        <v>8.693473111779351</v>
+      </c>
+      <c r="Q73">
+        <v>21.19347311177935</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1851104007906085</v>
+      </c>
+      <c r="T73">
+        <v>1.971540907037576</v>
+      </c>
+      <c r="U73">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W73">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.096711603795987</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1026347102929529</v>
+      </c>
+      <c r="C74">
+        <v>29.61578031884279</v>
+      </c>
+      <c r="D74">
+        <v>138.4136612458166</v>
+      </c>
+      <c r="E74">
+        <v>4.900824083954603</v>
+      </c>
+      <c r="F74">
+        <v>116.9978809269738</v>
+      </c>
+      <c r="G74">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H74">
+        <v>50.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>34.61</v>
+      </c>
+      <c r="K74">
+        <v>12.5</v>
+      </c>
+      <c r="L74">
+        <v>22.11</v>
+      </c>
+      <c r="M74">
+        <v>10.69360631672541</v>
+      </c>
+      <c r="N74">
+        <v>11.41639368327459</v>
+      </c>
+      <c r="O74">
+        <v>2.834566406955257</v>
+      </c>
+      <c r="P74">
+        <v>8.581827276319334</v>
+      </c>
+      <c r="Q74">
+        <v>21.08182727631933</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1898790038606585</v>
+      </c>
+      <c r="T74">
+        <v>2.035798102501646</v>
+      </c>
+      <c r="U74">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W74">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.06759060929882</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1028058788837159</v>
+      </c>
+      <c r="C75">
+        <v>27.81497212605073</v>
+      </c>
+      <c r="D75">
+        <v>138.2378236214548</v>
+      </c>
+      <c r="E75">
+        <v>6.525794652384803</v>
+      </c>
+      <c r="F75">
+        <v>118.622851495404</v>
+      </c>
+      <c r="G75">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H75">
+        <v>50.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>34.61</v>
+      </c>
+      <c r="K75">
+        <v>12.5</v>
+      </c>
+      <c r="L75">
+        <v>22.11</v>
+      </c>
+      <c r="M75">
+        <v>10.84212862667993</v>
+      </c>
+      <c r="N75">
+        <v>11.26787137332007</v>
+      </c>
+      <c r="O75">
+        <v>2.797689932460754</v>
+      </c>
+      <c r="P75">
+        <v>8.470181440859317</v>
+      </c>
+      <c r="Q75">
+        <v>20.97018144085932</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1950008367877492</v>
+      </c>
+      <c r="T75">
+        <v>2.104815090222313</v>
+      </c>
+      <c r="U75">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W75">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.039267450267329</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1029770474744789</v>
+      </c>
+      <c r="C76">
+        <v>26.01461012680716</v>
+      </c>
+      <c r="D76">
+        <v>138.0624321906414</v>
+      </c>
+      <c r="E76">
+        <v>8.150765220814989</v>
+      </c>
+      <c r="F76">
+        <v>120.2478220638342</v>
+      </c>
+      <c r="G76">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H76">
+        <v>50.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>34.61</v>
+      </c>
+      <c r="K76">
+        <v>12.5</v>
+      </c>
+      <c r="L76">
+        <v>22.11</v>
+      </c>
+      <c r="M76">
+        <v>10.99065093663445</v>
+      </c>
+      <c r="N76">
+        <v>11.11934906336555</v>
+      </c>
+      <c r="O76">
+        <v>2.760813457966252</v>
+      </c>
+      <c r="P76">
+        <v>8.3585356053993</v>
+      </c>
+      <c r="Q76">
+        <v>20.8585356053993</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2005166568630777</v>
+      </c>
+      <c r="T76">
+        <v>2.179141076998417</v>
+      </c>
+      <c r="U76">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W76">
+        <v>0.06870637390551181</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.011709782020474</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1150440406500858</v>
+      </c>
+      <c r="C77">
+        <v>13.05450573738736</v>
+      </c>
+      <c r="D77">
+        <v>126.7272983696518</v>
+      </c>
+      <c r="E77">
+        <v>9.775735789245189</v>
+      </c>
+      <c r="F77">
+        <v>121.8727926322644</v>
+      </c>
+      <c r="G77">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H77">
+        <v>50.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>34.61</v>
+      </c>
+      <c r="K77">
+        <v>12.5</v>
+      </c>
+      <c r="L77">
+        <v>22.11</v>
+      </c>
+      <c r="M77">
+        <v>13.71068917112975</v>
+      </c>
+      <c r="N77">
+        <v>8.399310828870254</v>
+      </c>
+      <c r="O77">
+        <v>2.08545754268892</v>
+      </c>
+      <c r="P77">
+        <v>6.313853286181335</v>
+      </c>
+      <c r="Q77">
+        <v>18.81385328618133</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2064737425444325</v>
+      </c>
+      <c r="T77">
+        <v>2.259413142716609</v>
+      </c>
+      <c r="U77">
+        <v>0.1125</v>
+      </c>
+      <c r="V77">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W77">
+        <v>0.08456747335197022</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>1.612610403753917</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1153738202353134</v>
+      </c>
+      <c r="C78">
+        <v>11.14582647213902</v>
+      </c>
+      <c r="D78">
+        <v>126.4435896728336</v>
+      </c>
+      <c r="E78">
+        <v>11.40070635767539</v>
+      </c>
+      <c r="F78">
+        <v>123.4977632006946</v>
+      </c>
+      <c r="G78">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H78">
+        <v>50.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>34.61</v>
+      </c>
+      <c r="K78">
+        <v>12.5</v>
+      </c>
+      <c r="L78">
+        <v>22.11</v>
+      </c>
+      <c r="M78">
+        <v>13.89349836007814</v>
+      </c>
+      <c r="N78">
+        <v>8.216501639921855</v>
+      </c>
+      <c r="O78">
+        <v>2.040068008983979</v>
+      </c>
+      <c r="P78">
+        <v>6.176433630937876</v>
+      </c>
+      <c r="Q78">
+        <v>18.67643363093788</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2129272520325668</v>
+      </c>
+      <c r="T78">
+        <v>2.34637454724465</v>
+      </c>
+      <c r="U78">
+        <v>0.1125</v>
+      </c>
+      <c r="V78">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W78">
+        <v>0.08456747335197022</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>1.591391845809786</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.115703599820541</v>
+      </c>
+      <c r="C79">
+        <v>9.238414665932382</v>
+      </c>
+      <c r="D79">
+        <v>126.1611484350572</v>
+      </c>
+      <c r="E79">
+        <v>13.02567692610558</v>
+      </c>
+      <c r="F79">
+        <v>125.1227337691248</v>
+      </c>
+      <c r="G79">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H79">
+        <v>50.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>34.61</v>
+      </c>
+      <c r="K79">
+        <v>12.5</v>
+      </c>
+      <c r="L79">
+        <v>22.11</v>
+      </c>
+      <c r="M79">
+        <v>14.07630754902654</v>
+      </c>
+      <c r="N79">
+        <v>8.03369245097346</v>
+      </c>
+      <c r="O79">
+        <v>1.994678475279039</v>
+      </c>
+      <c r="P79">
+        <v>6.039013975694421</v>
+      </c>
+      <c r="Q79">
+        <v>18.53901397569442</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2199419362587997</v>
+      </c>
+      <c r="T79">
+        <v>2.440897813035999</v>
+      </c>
+      <c r="U79">
+        <v>0.1125</v>
+      </c>
+      <c r="V79">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W79">
+        <v>0.08456747335197022</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>1.570724419240829</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1160333794057686</v>
+      </c>
+      <c r="C80">
+        <v>7.332261844201511</v>
+      </c>
+      <c r="D80">
+        <v>125.8799661817565</v>
+      </c>
+      <c r="E80">
+        <v>14.65064749453578</v>
+      </c>
+      <c r="F80">
+        <v>126.747704337555</v>
+      </c>
+      <c r="G80">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H80">
+        <v>50.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>34.61</v>
+      </c>
+      <c r="K80">
+        <v>12.5</v>
+      </c>
+      <c r="L80">
+        <v>22.11</v>
+      </c>
+      <c r="M80">
+        <v>14.25911673797494</v>
+      </c>
+      <c r="N80">
+        <v>7.850883262025063</v>
+      </c>
+      <c r="O80">
+        <v>1.949288941574098</v>
+      </c>
+      <c r="P80">
+        <v>5.901594320450965</v>
+      </c>
+      <c r="Q80">
+        <v>18.40159432045096</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2275943190510538</v>
+      </c>
+      <c r="T80">
+        <v>2.544014102990198</v>
+      </c>
+      <c r="U80">
+        <v>0.1125</v>
+      </c>
+      <c r="V80">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W80">
+        <v>0.08456747335197022</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>1.550586926686459</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1163631589909962</v>
+      </c>
+      <c r="C81">
+        <v>5.427359607763407</v>
+      </c>
+      <c r="D81">
+        <v>125.6000345137486</v>
+      </c>
+      <c r="E81">
+        <v>16.27561806296596</v>
+      </c>
+      <c r="F81">
+        <v>128.3726749059852</v>
+      </c>
+      <c r="G81">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H81">
+        <v>50.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>34.61</v>
+      </c>
+      <c r="K81">
+        <v>12.5</v>
+      </c>
+      <c r="L81">
+        <v>22.11</v>
+      </c>
+      <c r="M81">
+        <v>14.44192592692333</v>
+      </c>
+      <c r="N81">
+        <v>7.668074073076667</v>
+      </c>
+      <c r="O81">
+        <v>1.903899407869158</v>
+      </c>
+      <c r="P81">
+        <v>5.764174665207509</v>
+      </c>
+      <c r="Q81">
+        <v>18.26417466520751</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2359755002044751</v>
+      </c>
+      <c r="T81">
+        <v>2.656950991987654</v>
+      </c>
+      <c r="U81">
+        <v>0.1125</v>
+      </c>
+      <c r="V81">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W81">
+        <v>0.08456747335197022</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.530959244070174</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1166929385762238</v>
+      </c>
+      <c r="C82">
+        <v>3.523699631981628</v>
+      </c>
+      <c r="D82">
+        <v>125.321345106397</v>
+      </c>
+      <c r="E82">
+        <v>17.90058863139616</v>
+      </c>
+      <c r="F82">
+        <v>129.9976454744154</v>
+      </c>
+      <c r="G82">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H82">
+        <v>50.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>34.61</v>
+      </c>
+      <c r="K82">
+        <v>12.5</v>
+      </c>
+      <c r="L82">
+        <v>22.11</v>
+      </c>
+      <c r="M82">
+        <v>14.62473511587173</v>
+      </c>
+      <c r="N82">
+        <v>7.485264884128268</v>
+      </c>
+      <c r="O82">
+        <v>1.858509874164217</v>
+      </c>
+      <c r="P82">
+        <v>5.626755009964051</v>
+      </c>
+      <c r="Q82">
+        <v>18.12675500996405</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2451947994732384</v>
+      </c>
+      <c r="T82">
+        <v>2.781181569884856</v>
+      </c>
+      <c r="U82">
+        <v>0.1125</v>
+      </c>
+      <c r="V82">
+        <v>0.2482891257602647</v>
+      </c>
+      <c r="W82">
+        <v>0.08456747335197022</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>1.511822253519297</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1754939221076334</v>
+      </c>
+      <c r="C83">
+        <v>-33.62721458617018</v>
+      </c>
+      <c r="D83">
+        <v>89.79540145667539</v>
+      </c>
+      <c r="E83">
+        <v>19.52555919982636</v>
+      </c>
+      <c r="F83">
+        <v>131.6226160428456</v>
+      </c>
+      <c r="G83">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H83">
+        <v>50.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>34.61</v>
+      </c>
+      <c r="K83">
+        <v>12.5</v>
+      </c>
+      <c r="L83">
+        <v>22.11</v>
+      </c>
+      <c r="M83">
+        <v>25.87700631402344</v>
+      </c>
+      <c r="N83">
+        <v>-3.76700631402344</v>
+      </c>
+      <c r="O83">
+        <v>-0.9353067044422774</v>
+      </c>
+      <c r="P83">
+        <v>-2.831699609581163</v>
+      </c>
+      <c r="Q83">
+        <v>9.668300390418837</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2633217600760168</v>
+      </c>
+      <c r="T83">
+        <v>3.025443386922611</v>
+      </c>
+      <c r="U83">
+        <v>0.1966</v>
+      </c>
+      <c r="V83">
+        <v>0.2121448093315359</v>
+      </c>
+      <c r="W83">
+        <v>0.15489233048542</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8544265024976248</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1770719221076334</v>
+      </c>
+      <c r="C84">
+        <v>-35.93014766751318</v>
+      </c>
+      <c r="D84">
+        <v>89.11743894376256</v>
+      </c>
+      <c r="E84">
+        <v>21.15052976825653</v>
+      </c>
+      <c r="F84">
+        <v>133.2475866112758</v>
+      </c>
+      <c r="G84">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H84">
+        <v>50.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>34.61</v>
+      </c>
+      <c r="K84">
+        <v>12.5</v>
+      </c>
+      <c r="L84">
+        <v>22.11</v>
+      </c>
+      <c r="M84">
+        <v>26.19647552777681</v>
+      </c>
+      <c r="N84">
+        <v>-4.086475527776813</v>
+      </c>
+      <c r="O84">
+        <v>-1.014627436232421</v>
+      </c>
+      <c r="P84">
+        <v>-3.071848091544391</v>
+      </c>
+      <c r="Q84">
+        <v>9.428151908455609</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2757951911913511</v>
+      </c>
+      <c r="T84">
+        <v>3.193523575084978</v>
+      </c>
+      <c r="U84">
+        <v>0.1966</v>
+      </c>
+      <c r="V84">
+        <v>0.2095576775104196</v>
+      </c>
+      <c r="W84">
+        <v>0.1554009606014515</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.8440066671013123</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1786499221076334</v>
+      </c>
+      <c r="C85">
+        <v>-38.22292011927971</v>
+      </c>
+      <c r="D85">
+        <v>88.44963706042624</v>
+      </c>
+      <c r="E85">
+        <v>22.77550033668673</v>
+      </c>
+      <c r="F85">
+        <v>134.872557179706</v>
+      </c>
+      <c r="G85">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H85">
+        <v>50.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>34.61</v>
+      </c>
+      <c r="K85">
+        <v>12.5</v>
+      </c>
+      <c r="L85">
+        <v>22.11</v>
+      </c>
+      <c r="M85">
+        <v>26.51594474153019</v>
+      </c>
+      <c r="N85">
+        <v>-4.405944741530188</v>
+      </c>
+      <c r="O85">
+        <v>-1.093948168022566</v>
+      </c>
+      <c r="P85">
+        <v>-3.311996573507622</v>
+      </c>
+      <c r="Q85">
+        <v>9.188003426492378</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2897360847908423</v>
+      </c>
+      <c r="T85">
+        <v>3.381377903031153</v>
+      </c>
+      <c r="U85">
+        <v>0.1966</v>
+      </c>
+      <c r="V85">
+        <v>0.2070328862151134</v>
+      </c>
+      <c r="W85">
+        <v>0.1558973345701087</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.8338379120759953</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1802279221076334</v>
+      </c>
+      <c r="C86">
+        <v>-40.50575865871767</v>
+      </c>
+      <c r="D86">
+        <v>87.79176908941845</v>
+      </c>
+      <c r="E86">
+        <v>24.4004709051169</v>
+      </c>
+      <c r="F86">
+        <v>136.4975277481361</v>
+      </c>
+      <c r="G86">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H86">
+        <v>50.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>34.61</v>
+      </c>
+      <c r="K86">
+        <v>12.5</v>
+      </c>
+      <c r="L86">
+        <v>22.11</v>
+      </c>
+      <c r="M86">
+        <v>26.83541395528356</v>
+      </c>
+      <c r="N86">
+        <v>-4.72541395528356</v>
+      </c>
+      <c r="O86">
+        <v>-1.17326889981271</v>
+      </c>
+      <c r="P86">
+        <v>-3.55214505547085</v>
+      </c>
+      <c r="Q86">
+        <v>8.94785494452915</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3054195900902699</v>
+      </c>
+      <c r="T86">
+        <v>3.592714021970599</v>
+      </c>
+      <c r="U86">
+        <v>0.1966</v>
+      </c>
+      <c r="V86">
+        <v>0.2045682089982668</v>
+      </c>
+      <c r="W86">
+        <v>0.1563818901109408</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.8239112702655669</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1818059221076334</v>
+      </c>
+      <c r="C87">
+        <v>-42.77888330779085</v>
+      </c>
+      <c r="D87">
+        <v>87.14361500877547</v>
+      </c>
+      <c r="E87">
+        <v>26.0254414735471</v>
+      </c>
+      <c r="F87">
+        <v>138.1224983165663</v>
+      </c>
+      <c r="G87">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H87">
+        <v>50.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>34.61</v>
+      </c>
+      <c r="K87">
+        <v>12.5</v>
+      </c>
+      <c r="L87">
+        <v>22.11</v>
+      </c>
+      <c r="M87">
+        <v>27.15488316903694</v>
+      </c>
+      <c r="N87">
+        <v>-5.04488316903694</v>
+      </c>
+      <c r="O87">
+        <v>-1.252589631602856</v>
+      </c>
+      <c r="P87">
+        <v>-3.792293537434084</v>
+      </c>
+      <c r="Q87">
+        <v>8.707706462565916</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3231942294296212</v>
+      </c>
+      <c r="T87">
+        <v>3.832228290101973</v>
+      </c>
+      <c r="U87">
+        <v>0.1966</v>
+      </c>
+      <c r="V87">
+        <v>0.2021615241865225</v>
+      </c>
+      <c r="W87">
+        <v>0.1568550443449297</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.8142181964977366</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1833839221076334</v>
+      </c>
+      <c r="C88">
+        <v>-45.04250763851923</v>
+      </c>
+      <c r="D88">
+        <v>86.50496124647729</v>
+      </c>
+      <c r="E88">
+        <v>27.6504120419773</v>
+      </c>
+      <c r="F88">
+        <v>139.7474688849965</v>
+      </c>
+      <c r="G88">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H88">
+        <v>50.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>34.61</v>
+      </c>
+      <c r="K88">
+        <v>12.5</v>
+      </c>
+      <c r="L88">
+        <v>22.11</v>
+      </c>
+      <c r="M88">
+        <v>27.47435238279031</v>
+      </c>
+      <c r="N88">
+        <v>-5.364352382790315</v>
+      </c>
+      <c r="O88">
+        <v>-1.331910363393</v>
+      </c>
+      <c r="P88">
+        <v>-4.032442019397315</v>
+      </c>
+      <c r="Q88">
+        <v>8.467557980602685</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3435081029603084</v>
+      </c>
+      <c r="T88">
+        <v>4.105958882252113</v>
+      </c>
+      <c r="U88">
+        <v>0.1966</v>
+      </c>
+      <c r="V88">
+        <v>0.1998108087890048</v>
+      </c>
+      <c r="W88">
+        <v>0.1573171949920817</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.8047505430500885</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2006380115478085</v>
+      </c>
+      <c r="C89">
+        <v>-53.08516424606125</v>
+      </c>
+      <c r="D89">
+        <v>80.08727520736547</v>
+      </c>
+      <c r="E89">
+        <v>29.2753826104075</v>
+      </c>
+      <c r="F89">
+        <v>141.3724394534267</v>
+      </c>
+      <c r="G89">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H89">
+        <v>50.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>34.61</v>
+      </c>
+      <c r="K89">
+        <v>12.5</v>
+      </c>
+      <c r="L89">
+        <v>22.11</v>
+      </c>
+      <c r="M89">
+        <v>30.22542755514263</v>
+      </c>
+      <c r="N89">
+        <v>-8.115427555142631</v>
+      </c>
+      <c r="O89">
+        <v>-2.014972412837126</v>
+      </c>
+      <c r="P89">
+        <v>-6.100455142305504</v>
+      </c>
+      <c r="Q89">
+        <v>6.399544857694496</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3724247988816789</v>
+      </c>
+      <c r="T89">
+        <v>4.495612991579165</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.1816243148436597</v>
+      </c>
+      <c r="W89">
+        <v>0.1749687214864256</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.7315032999835316</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2023880115478085</v>
+      </c>
+      <c r="C90">
+        <v>-55.30825893127398</v>
+      </c>
+      <c r="D90">
+        <v>79.48915109058291</v>
+      </c>
+      <c r="E90">
+        <v>30.90035317883768</v>
+      </c>
+      <c r="F90">
+        <v>142.9974100218569</v>
+      </c>
+      <c r="G90">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H90">
+        <v>50.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>34.61</v>
+      </c>
+      <c r="K90">
+        <v>12.5</v>
+      </c>
+      <c r="L90">
+        <v>22.11</v>
+      </c>
+      <c r="M90">
+        <v>30.572846262673</v>
+      </c>
+      <c r="N90">
+        <v>-8.462846262673004</v>
+      </c>
+      <c r="O90">
+        <v>-2.101232700002604</v>
+      </c>
+      <c r="P90">
+        <v>-6.3616135626704</v>
+      </c>
+      <c r="Q90">
+        <v>6.1383864373296</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4002268654551522</v>
+      </c>
+      <c r="T90">
+        <v>4.870247407544096</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.1795604021749818</v>
+      </c>
+      <c r="W90">
+        <v>0.1754099860149889</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.7231907624837187</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2041380115478085</v>
+      </c>
+      <c r="C91">
+        <v>-57.52248578012292</v>
+      </c>
+      <c r="D91">
+        <v>78.89989481016417</v>
+      </c>
+      <c r="E91">
+        <v>32.52532374726788</v>
+      </c>
+      <c r="F91">
+        <v>144.6223805902871</v>
+      </c>
+      <c r="G91">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H91">
+        <v>50.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>34.61</v>
+      </c>
+      <c r="K91">
+        <v>12.5</v>
+      </c>
+      <c r="L91">
+        <v>22.11</v>
+      </c>
+      <c r="M91">
+        <v>30.92026497020338</v>
+      </c>
+      <c r="N91">
+        <v>-8.810264970203381</v>
+      </c>
+      <c r="O91">
+        <v>-2.187492987168082</v>
+      </c>
+      <c r="P91">
+        <v>-6.622771983035299</v>
+      </c>
+      <c r="Q91">
+        <v>5.877228016964701</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4330838532238024</v>
+      </c>
+      <c r="T91">
+        <v>5.312997171866287</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.1775428695662741</v>
+      </c>
+      <c r="W91">
+        <v>0.1758413344867306</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.7150650235794072</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2058880115478085</v>
+      </c>
+      <c r="C92">
+        <v>-59.72804055430379</v>
+      </c>
+      <c r="D92">
+        <v>78.3193106044135</v>
+      </c>
+      <c r="E92">
+        <v>34.15029431569808</v>
+      </c>
+      <c r="F92">
+        <v>146.2473511587173</v>
+      </c>
+      <c r="G92">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H92">
+        <v>50.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>34.61</v>
+      </c>
+      <c r="K92">
+        <v>12.5</v>
+      </c>
+      <c r="L92">
+        <v>22.11</v>
+      </c>
+      <c r="M92">
+        <v>31.26768367773376</v>
+      </c>
+      <c r="N92">
+        <v>-9.157683677733758</v>
+      </c>
+      <c r="O92">
+        <v>-2.27375327433356</v>
+      </c>
+      <c r="P92">
+        <v>-6.883930403400197</v>
+      </c>
+      <c r="Q92">
+        <v>5.616069596599803</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4725122385461827</v>
+      </c>
+      <c r="T92">
+        <v>5.844296889052916</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.1755701710155377</v>
+      </c>
+      <c r="W92">
+        <v>0.176263097436878</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.7071198566507471</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2076380115478085</v>
+      </c>
+      <c r="C93">
+        <v>-61.92511329555926</v>
+      </c>
+      <c r="D93">
+        <v>77.74720843158823</v>
+      </c>
+      <c r="E93">
+        <v>35.77526488412828</v>
+      </c>
+      <c r="F93">
+        <v>147.8723217271475</v>
+      </c>
+      <c r="G93">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H93">
+        <v>50.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>34.61</v>
+      </c>
+      <c r="K93">
+        <v>12.5</v>
+      </c>
+      <c r="L93">
+        <v>22.11</v>
+      </c>
+      <c r="M93">
+        <v>31.61510238526413</v>
+      </c>
+      <c r="N93">
+        <v>-9.505102385264134</v>
+      </c>
+      <c r="O93">
+        <v>-2.360013561499039</v>
+      </c>
+      <c r="P93">
+        <v>-7.145088823765095</v>
+      </c>
+      <c r="Q93">
+        <v>5.354911176234905</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5207024872735364</v>
+      </c>
+      <c r="T93">
+        <v>6.493663210058796</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.1736408284769054</v>
+      </c>
+      <c r="W93">
+        <v>0.1766755908716376</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.6993493087754641</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2093880115478085</v>
+      </c>
+      <c r="C94">
+        <v>-64.11388853307817</v>
+      </c>
+      <c r="D94">
+        <v>77.18340376249949</v>
+      </c>
+      <c r="E94">
+        <v>37.40023545255845</v>
+      </c>
+      <c r="F94">
+        <v>149.4972922955777</v>
+      </c>
+      <c r="G94">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H94">
+        <v>50.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>34.61</v>
+      </c>
+      <c r="K94">
+        <v>12.5</v>
+      </c>
+      <c r="L94">
+        <v>22.11</v>
+      </c>
+      <c r="M94">
+        <v>31.9625210927945</v>
+      </c>
+      <c r="N94">
+        <v>-9.852521092794504</v>
+      </c>
+      <c r="O94">
+        <v>-2.446273848664516</v>
+      </c>
+      <c r="P94">
+        <v>-7.406247244129988</v>
+      </c>
+      <c r="Q94">
+        <v>5.093752755870012</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5809402981827285</v>
+      </c>
+      <c r="T94">
+        <v>7.305371111316148</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.1717534281673739</v>
+      </c>
+      <c r="W94">
+        <v>0.1770791170578155</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.6917476858539918</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2111380115478085</v>
+      </c>
+      <c r="C95">
+        <v>-66.29454548193499</v>
+      </c>
+      <c r="D95">
+        <v>76.62771738207287</v>
+      </c>
+      <c r="E95">
+        <v>39.02520602098865</v>
+      </c>
+      <c r="F95">
+        <v>151.1222628640079</v>
+      </c>
+      <c r="G95">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H95">
+        <v>50.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>34.61</v>
+      </c>
+      <c r="K95">
+        <v>12.5</v>
+      </c>
+      <c r="L95">
+        <v>22.11</v>
+      </c>
+      <c r="M95">
+        <v>32.30993980032488</v>
+      </c>
+      <c r="N95">
+        <v>-10.19993980032488</v>
+      </c>
+      <c r="O95">
+        <v>-2.532534135829993</v>
+      </c>
+      <c r="P95">
+        <v>-7.667405664494884</v>
+      </c>
+      <c r="Q95">
+        <v>4.832594335505116</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6583889122088327</v>
+      </c>
+      <c r="T95">
+        <v>8.348995555789884</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.1699066171118107</v>
+      </c>
+      <c r="W95">
+        <v>0.1774739652614949</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.6843095386942715</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2128880115478085</v>
+      </c>
+      <c r="C96">
+        <v>-68.46725823301888</v>
+      </c>
+      <c r="D96">
+        <v>76.07997519941918</v>
+      </c>
+      <c r="E96">
+        <v>40.65017658941885</v>
+      </c>
+      <c r="F96">
+        <v>152.7472334324381</v>
+      </c>
+      <c r="G96">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H96">
+        <v>50.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>34.61</v>
+      </c>
+      <c r="K96">
+        <v>12.5</v>
+      </c>
+      <c r="L96">
+        <v>22.11</v>
+      </c>
+      <c r="M96">
+        <v>32.65735850785526</v>
+      </c>
+      <c r="N96">
+        <v>-10.54735850785526</v>
+      </c>
+      <c r="O96">
+        <v>-2.618794422995472</v>
+      </c>
+      <c r="P96">
+        <v>-7.928564084859785</v>
+      </c>
+      <c r="Q96">
+        <v>4.571435915140215</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7616537309103049</v>
+      </c>
+      <c r="T96">
+        <v>9.7404948150882</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.1680990999084936</v>
+      </c>
+      <c r="W96">
+        <v>0.1778604124395641</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.6770296499847579</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2146380115478085</v>
+      </c>
+      <c r="C97">
+        <v>-70.63219593487469</v>
+      </c>
+      <c r="D97">
+        <v>75.54000806599358</v>
+      </c>
+      <c r="E97">
+        <v>42.27514715784905</v>
+      </c>
+      <c r="F97">
+        <v>154.3722040008683</v>
+      </c>
+      <c r="G97">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H97">
+        <v>50.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>34.61</v>
+      </c>
+      <c r="K97">
+        <v>12.5</v>
+      </c>
+      <c r="L97">
+        <v>22.11</v>
+      </c>
+      <c r="M97">
+        <v>33.00477721538564</v>
+      </c>
+      <c r="N97">
+        <v>-10.89477721538564</v>
+      </c>
+      <c r="O97">
+        <v>-2.705054710160951</v>
+      </c>
+      <c r="P97">
+        <v>-8.189722505224687</v>
+      </c>
+      <c r="Q97">
+        <v>4.310277494775313</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9062244770923666</v>
+      </c>
+      <c r="T97">
+        <v>11.68859377810585</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.1663296356989304</v>
+      </c>
+      <c r="W97">
+        <v>0.1782387238875687</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.6699030220901814</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2163880115478085</v>
+      </c>
+      <c r="C98">
+        <v>-72.78952296785489</v>
+      </c>
+      <c r="D98">
+        <v>75.00765160144354</v>
+      </c>
+      <c r="E98">
+        <v>43.90011772627922</v>
+      </c>
+      <c r="F98">
+        <v>155.9971745692984</v>
+      </c>
+      <c r="G98">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H98">
+        <v>50.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>34.61</v>
+      </c>
+      <c r="K98">
+        <v>12.5</v>
+      </c>
+      <c r="L98">
+        <v>22.11</v>
+      </c>
+      <c r="M98">
+        <v>33.352195922916</v>
+      </c>
+      <c r="N98">
+        <v>-11.242195922916</v>
+      </c>
+      <c r="O98">
+        <v>-2.791314997326427</v>
+      </c>
+      <c r="P98">
+        <v>-8.450880925589576</v>
+      </c>
+      <c r="Q98">
+        <v>4.049119074410424</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.123080596365456</v>
+      </c>
+      <c r="T98">
+        <v>14.61074222263228</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.1645970353270666</v>
+      </c>
+      <c r="W98">
+        <v>0.1786091538470732</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.6629248656100755</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2181380115478085</v>
+      </c>
+      <c r="C99">
+        <v>-74.9393991109595</v>
+      </c>
+      <c r="D99">
+        <v>74.48274602676914</v>
+      </c>
+      <c r="E99">
+        <v>45.52508829470942</v>
+      </c>
+      <c r="F99">
+        <v>157.6221451377286</v>
+      </c>
+      <c r="G99">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H99">
+        <v>50.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>34.61</v>
+      </c>
+      <c r="K99">
+        <v>12.5</v>
+      </c>
+      <c r="L99">
+        <v>22.11</v>
+      </c>
+      <c r="M99">
+        <v>33.69961463044638</v>
+      </c>
+      <c r="N99">
+        <v>-11.58961463044638</v>
+      </c>
+      <c r="O99">
+        <v>-2.877575284491906</v>
+      </c>
+      <c r="P99">
+        <v>-8.712039345954478</v>
+      </c>
+      <c r="Q99">
+        <v>3.787960654045522</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.484507461820608</v>
+      </c>
+      <c r="T99">
+        <v>19.48098963017637</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.1629001586742103</v>
+      </c>
+      <c r="W99">
+        <v>0.1789719460754538</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.656090588645023</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2198880115478085</v>
+      </c>
+      <c r="C100">
+        <v>-77.08197970171882</v>
+      </c>
+      <c r="D100">
+        <v>73.96513600443998</v>
+      </c>
+      <c r="E100">
+        <v>47.15005886313959</v>
+      </c>
+      <c r="F100">
+        <v>159.2471157061588</v>
+      </c>
+      <c r="G100">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H100">
+        <v>50.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>34.61</v>
+      </c>
+      <c r="K100">
+        <v>12.5</v>
+      </c>
+      <c r="L100">
+        <v>22.11</v>
+      </c>
+      <c r="M100">
+        <v>34.04703333797675</v>
+      </c>
+      <c r="N100">
+        <v>-11.93703333797675</v>
+      </c>
+      <c r="O100">
+        <v>-2.963835571657382</v>
+      </c>
+      <c r="P100">
+        <v>-8.973197766319368</v>
+      </c>
+      <c r="Q100">
+        <v>3.526802233680632</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.207361192730911</v>
+      </c>
+      <c r="T100">
+        <v>29.22148444526455</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.1612379121571265</v>
+      </c>
+      <c r="W100">
+        <v>0.1793273343808063</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.649395786720074</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2216380115478085</v>
+      </c>
+      <c r="C101">
+        <v>-79.21741578945635</v>
+      </c>
+      <c r="D101">
+        <v>73.45467048513265</v>
+      </c>
+      <c r="E101">
+        <v>48.77502943156979</v>
+      </c>
+      <c r="F101">
+        <v>160.872086274589</v>
+      </c>
+      <c r="G101">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H101">
+        <v>50.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>34.61</v>
+      </c>
+      <c r="K101">
+        <v>12.5</v>
+      </c>
+      <c r="L101">
+        <v>22.11</v>
+      </c>
+      <c r="M101">
+        <v>34.39445204550713</v>
+      </c>
+      <c r="N101">
+        <v>-12.28445204550713</v>
+      </c>
+      <c r="O101">
+        <v>-3.050095858822861</v>
+      </c>
+      <c r="P101">
+        <v>-9.23435618668427</v>
+      </c>
+      <c r="Q101">
+        <v>3.26564381331573</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.375922385461823</v>
+      </c>
+      <c r="T101">
+        <v>58.44296889052909</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.1596092463777616</v>
+      </c>
+      <c r="W101">
+        <v>0.1796755431244346</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.6428362333188611</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
